--- a/data/leagues/Fantasy 2026 2026.xlsx
+++ b/data/leagues/Fantasy 2026 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="103">
   <si>
     <t>Fumbledore</t>
   </si>
@@ -55,13 +55,16 @@
     <t>Amanda's Awesome Team</t>
   </si>
   <si>
-    <t>1-1-0</t>
-  </si>
-  <si>
-    <t>2-0-0</t>
-  </si>
-  <si>
-    <t>0-2-0</t>
+    <t>2-1-0</t>
+  </si>
+  <si>
+    <t>1-2-0</t>
+  </si>
+  <si>
+    <t>3-0-0</t>
+  </si>
+  <si>
+    <t>0-3-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -124,6 +127,9 @@
     <t>Week_3</t>
   </si>
   <si>
+    <t>Week_4</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -145,33 +151,33 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Hilary Manion</t>
+  </si>
+  <si>
+    <t>Meghan Bishop</t>
+  </si>
+  <si>
     <t>Michele Schul</t>
   </si>
   <si>
+    <t>kaitlin hahn</t>
+  </si>
+  <si>
+    <t>chloe melvin</t>
+  </si>
+  <si>
+    <t>ashley Lavery</t>
+  </si>
+  <si>
     <t>Marianne Schulmeister</t>
   </si>
   <si>
-    <t>kaitlin hahn</t>
-  </si>
-  <si>
-    <t>chloe melvin</t>
-  </si>
-  <si>
-    <t>Meghan Bishop</t>
-  </si>
-  <si>
     <t>Amanda Pasquale</t>
   </si>
   <si>
-    <t>ashley Lavery</t>
-  </si>
-  <si>
     <t>Madison Dietz</t>
   </si>
   <si>
-    <t>Hilary Manion</t>
-  </si>
-  <si>
     <t>Shannon Finegan</t>
   </si>
   <si>
@@ -199,64 +205,70 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>11.1-2.8-0.1</t>
-  </si>
-  <si>
-    <t>10.5-3.5-0.1</t>
-  </si>
-  <si>
-    <t>8.6-5.3-0.1</t>
-  </si>
-  <si>
-    <t>8.4-5.5-0.1</t>
-  </si>
-  <si>
-    <t>7.7-6.2-0.1</t>
-  </si>
-  <si>
-    <t>5.7-8.1-0.1</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>11.2-2.7-0.1</t>
+  </si>
+  <si>
+    <t>10.0-3.9-0.1</t>
+  </si>
+  <si>
+    <t>8.7-5.2-0.1</t>
+  </si>
+  <si>
+    <t>7.9-5.9-0.1</t>
+  </si>
+  <si>
+    <t>7.5-6.4-0.1</t>
+  </si>
+  <si>
+    <t>5.8-8.0-0.1</t>
   </si>
   <si>
     <t>5.4-8.5-0.1</t>
   </si>
   <si>
-    <t>5.1-8.8-0.1</t>
-  </si>
-  <si>
-    <t>3.8-10.1-0.1</t>
-  </si>
-  <si>
-    <t>3.3-10.6-0.1</t>
+    <t>5.2-8.7-0.1</t>
+  </si>
+  <si>
+    <t>5.0-8.8-0.1</t>
+  </si>
+  <si>
+    <t>2.8-11.1-0.1</t>
   </si>
   <si>
     <t>11-3</t>
   </si>
   <si>
+    <t>10-4</t>
+  </si>
+  <si>
     <t>9-5</t>
   </si>
   <si>
     <t>8-6</t>
   </si>
   <si>
+    <t>7-7</t>
+  </si>
+  <si>
     <t>6-8</t>
   </si>
   <si>
     <t>5-9</t>
   </si>
   <si>
-    <t>4-10</t>
-  </si>
-  <si>
-    <t>3-11</t>
+    <t>2-12</t>
   </si>
   <si>
     <t>Owners</t>
@@ -268,10 +280,13 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↑3</t>
+    <t>↑1</t>
+  </si>
+  <si>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↓3</t>
   </si>
   <si>
     <t>↓1</t>
@@ -280,12 +295,12 @@
     <t>0</t>
   </si>
   <si>
+    <t>↑4</t>
+  </si>
+  <si>
     <t>↓5</t>
   </si>
   <si>
-    <t>↑1</t>
-  </si>
-  <si>
     <t>↓2</t>
   </si>
   <si>
@@ -293,6 +308,9 @@
   </si>
   <si>
     <t>Week 2</t>
+  </si>
+  <si>
+    <t>Week 3</t>
   </si>
   <si>
     <t>Week</t>
@@ -714,13 +732,13 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -735,7 +753,7 @@
         <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K2" t="s">
         <v>10</v>
@@ -746,34 +764,34 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -781,31 +799,31 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
         <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
         <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K4" t="s">
         <v>10</v>
@@ -819,28 +837,28 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>10</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K5" t="s">
         <v>10</v>
@@ -854,13 +872,13 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>10</v>
@@ -872,7 +890,7 @@
         <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J6" t="s">
         <v>10</v>
@@ -886,34 +904,34 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -921,31 +939,31 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K8" t="s">
         <v>10</v>
@@ -959,7 +977,7 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -971,19 +989,19 @@
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -991,34 +1009,34 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1032,28 +1050,28 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
         <v>10</v>
       </c>
       <c r="G11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I11" t="s">
         <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1063,30 +1081,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1139,6 +1157,32 @@
       </c>
       <c r="H3" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1153,13 +1197,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1170,10 +1214,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1181,13 +1225,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1195,13 +1239,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1209,13 +1253,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1223,13 +1267,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1237,10 +1281,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -1254,10 +1298,10 @@
         <v>9</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1268,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1279,13 +1323,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1296,7 +1340,7 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -1314,16 +1358,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1334,13 +1378,13 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="D2">
-        <v>-0.3999999999999999</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1351,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -1365,13 +1409,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="D4">
-        <v>0.3</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1385,10 +1429,10 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="D5">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1402,13 +1446,13 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1416,16 +1460,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1433,16 +1477,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="D8">
-        <v>-0.09999999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1450,16 +1494,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C9">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="D9">
-        <v>-0.2</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1467,16 +1511,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="D10">
-        <v>0.5</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1484,16 +1528,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C11">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D11">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1508,40 +1552,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1549,19 +1593,19 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>50.8</v>
+        <v>61.4</v>
       </c>
       <c r="C2">
-        <v>36.2</v>
+        <v>29.6</v>
       </c>
       <c r="D2">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1573,13 +1617,13 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1587,29 +1631,29 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <v>41.6</v>
+        <v>32</v>
       </c>
       <c r="C3">
-        <v>35.7</v>
+        <v>38.2</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="E3">
-        <v>5.4</v>
+        <v>7.5</v>
       </c>
       <c r="F3">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="G3">
+        <v>0.6</v>
+      </c>
+      <c r="H3">
+        <v>0.6</v>
+      </c>
+      <c r="I3">
         <v>0.3</v>
       </c>
-      <c r="H3">
-        <v>0.2</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
       <c r="J3">
         <v>0</v>
       </c>
@@ -1617,240 +1661,240 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>99.8</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="C4">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="D4">
-        <v>25.5</v>
+        <v>34.9</v>
       </c>
       <c r="E4">
-        <v>27.9</v>
+        <v>20.4</v>
       </c>
       <c r="F4">
-        <v>20.4</v>
+        <v>13.4</v>
       </c>
       <c r="G4">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="H4">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="I4">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J4">
         <v>0.2</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L4">
-        <v>96.2</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="C5">
-        <v>10.4</v>
+        <v>7.7</v>
       </c>
       <c r="D5">
-        <v>28.8</v>
+        <v>18.7</v>
       </c>
       <c r="E5">
-        <v>24.6</v>
+        <v>28.1</v>
       </c>
       <c r="F5">
-        <v>19.9</v>
+        <v>21.6</v>
       </c>
       <c r="G5">
-        <v>8.199999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="H5">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>95.2</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="D6">
-        <v>17.6</v>
+        <v>14.1</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>23.8</v>
       </c>
       <c r="F6">
-        <v>27.4</v>
+        <v>25.2</v>
       </c>
       <c r="G6">
-        <v>13</v>
+        <v>15.8</v>
       </c>
       <c r="H6">
-        <v>5.9</v>
+        <v>10.1</v>
       </c>
       <c r="I6">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J6">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="K6">
         <v>0.2</v>
       </c>
       <c r="L6">
-        <v>90.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C7">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="D7">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="E7">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="F7">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="G7">
-        <v>26.8</v>
+        <v>20</v>
       </c>
       <c r="H7">
-        <v>22.9</v>
+        <v>21.9</v>
       </c>
       <c r="I7">
-        <v>16.6</v>
+        <v>17.9</v>
       </c>
       <c r="J7">
-        <v>10.3</v>
+        <v>12.7</v>
       </c>
       <c r="K7">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="L7">
-        <v>47.5</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D8">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="E8">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="F8">
-        <v>7.8</v>
+        <v>9.5</v>
       </c>
       <c r="G8">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="H8">
-        <v>24.1</v>
+        <v>21</v>
       </c>
       <c r="I8">
-        <v>22.5</v>
+        <v>23.2</v>
       </c>
       <c r="J8">
-        <v>15.3</v>
+        <v>16.5</v>
       </c>
       <c r="K8">
-        <v>6.7</v>
+        <v>5.1</v>
       </c>
       <c r="L8">
-        <v>31.4</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="E9">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="F9">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="G9">
-        <v>15.7</v>
+        <v>13.2</v>
       </c>
       <c r="H9">
-        <v>22.5</v>
+        <v>19.1</v>
       </c>
       <c r="I9">
-        <v>24.2</v>
+        <v>22.7</v>
       </c>
       <c r="J9">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="K9">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="L9">
-        <v>27.3</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1859,31 +1903,31 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="E10">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="F10">
-        <v>1.4</v>
+        <v>6.7</v>
       </c>
       <c r="G10">
-        <v>4.6</v>
+        <v>13.7</v>
       </c>
       <c r="H10">
-        <v>11.8</v>
+        <v>16.4</v>
       </c>
       <c r="I10">
-        <v>18.8</v>
+        <v>22.4</v>
       </c>
       <c r="J10">
-        <v>26.4</v>
+        <v>25.8</v>
       </c>
       <c r="K10">
-        <v>35.7</v>
+        <v>10.5</v>
       </c>
       <c r="L10">
-        <v>7.3</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1900,28 +1944,28 @@
         <v>0</v>
       </c>
       <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>0.2</v>
       </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
       <c r="G11">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="H11">
-        <v>6.8</v>
+        <v>2.2</v>
       </c>
       <c r="I11">
-        <v>13.3</v>
+        <v>6.7</v>
       </c>
       <c r="J11">
-        <v>28.3</v>
+        <v>18.4</v>
       </c>
       <c r="K11">
-        <v>47.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="L11">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
     </row>
   </sheetData>
@@ -1931,35 +1975,41 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
       <c r="D2">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="E2">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1970,119 +2020,146 @@
         <v>99.8</v>
       </c>
       <c r="D3">
-        <v>99.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="E3">
+        <v>99.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>43.2</v>
+      </c>
+      <c r="C4">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="D4">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="E4">
+        <v>96.89999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>67.5</v>
-      </c>
-      <c r="C4">
-        <v>94.3</v>
-      </c>
-      <c r="D4">
-        <v>94.69999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="B5">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C5">
-        <v>96.8</v>
+        <v>95.39999999999999</v>
       </c>
       <c r="D5">
-        <v>94.19999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>90.60000000000001</v>
+      </c>
+      <c r="E5">
+        <v>90.40000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>95.5</v>
+      </c>
+      <c r="C6">
+        <v>51.7</v>
+      </c>
+      <c r="D6">
+        <v>84.39999999999999</v>
+      </c>
+      <c r="E6">
+        <v>83.59999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>50</v>
+      </c>
+      <c r="C7">
+        <v>4.5</v>
+      </c>
+      <c r="D7">
+        <v>44.9</v>
+      </c>
+      <c r="E7">
+        <v>42.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>50.2</v>
-      </c>
-      <c r="C6">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="D6">
-        <v>91.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>95.8</v>
-      </c>
-      <c r="C7">
-        <v>50.2</v>
-      </c>
-      <c r="D7">
-        <v>49.9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="B8">
+        <v>55.50000000000001</v>
+      </c>
+      <c r="C8">
+        <v>90.2</v>
+      </c>
+      <c r="D8">
+        <v>32.8</v>
+      </c>
+      <c r="E8">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="C8">
-        <v>35.09999999999999</v>
-      </c>
-      <c r="D8">
-        <v>33.90000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="B9">
+        <v>85.5</v>
+      </c>
+      <c r="C9">
+        <v>31.5</v>
+      </c>
+      <c r="D9">
+        <v>26.2</v>
+      </c>
+      <c r="E9">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>0.2</v>
       </c>
-      <c r="C9">
-        <v>27</v>
-      </c>
-      <c r="D9">
-        <v>26.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10">
-        <v>51.6</v>
-      </c>
       <c r="C10">
-        <v>5.600000000000001</v>
+        <v>28.4</v>
       </c>
       <c r="D10">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>22.2</v>
+      </c>
+      <c r="E10">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B11">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="C11">
+        <v>2.9</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
         <v>2.3</v>
-      </c>
-      <c r="D11">
-        <v>3.9</v>
       </c>
     </row>
   </sheetData>
@@ -2097,28 +2174,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2126,28 +2203,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D2">
-        <v>127.29</v>
+        <v>101.93</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>116.19</v>
+        <v>120.25</v>
       </c>
       <c r="G2">
-        <v>0.458</v>
+        <v>0.545</v>
       </c>
       <c r="H2">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2155,28 +2232,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>118.83</v>
+        <v>110.71</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3">
-        <v>114.71</v>
+        <v>119.45</v>
       </c>
       <c r="G3">
-        <v>0.375</v>
+        <v>0.515</v>
       </c>
       <c r="H3">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2184,28 +2261,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4">
-        <v>150.25</v>
+        <v>125.72</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4">
-        <v>116.83</v>
+        <v>117.24</v>
       </c>
       <c r="G4">
-        <v>0.542</v>
+        <v>0.455</v>
       </c>
       <c r="H4">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="I4">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2213,28 +2290,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D5">
-        <v>111.79</v>
+        <v>141.6</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5">
-        <v>121.79</v>
+        <v>119.04</v>
       </c>
       <c r="G5">
+        <v>0.545</v>
+      </c>
+      <c r="H5">
         <v>0.5</v>
       </c>
-      <c r="H5">
-        <v>0.3</v>
-      </c>
       <c r="I5">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2242,28 +2319,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D6">
-        <v>106.72</v>
+        <v>119.49</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6">
-        <v>120.46</v>
+        <v>120.51</v>
       </c>
       <c r="G6">
-        <v>0.458</v>
+        <v>0.485</v>
       </c>
       <c r="H6">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2271,28 +2348,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7">
-        <v>143.59</v>
+        <v>113.68</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7">
-        <v>119.11</v>
+        <v>122.15</v>
       </c>
       <c r="G7">
-        <v>0.458</v>
+        <v>0.576</v>
       </c>
       <c r="H7">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2300,28 +2377,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8">
-        <v>126.29</v>
+        <v>119.47</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8">
-        <v>120.54</v>
+        <v>116.74</v>
       </c>
       <c r="G8">
-        <v>0.542</v>
+        <v>0.424</v>
       </c>
       <c r="H8">
-        <v>-0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="I8">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2329,28 +2406,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9">
-        <v>106.28</v>
+        <v>138.83</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>122.79</v>
+        <v>119.02</v>
       </c>
       <c r="G9">
-        <v>0.583</v>
+        <v>0.455</v>
       </c>
       <c r="H9">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2358,28 +2435,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D10">
-        <v>98.92</v>
+        <v>108.9</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10">
-        <v>119.78</v>
+        <v>120.82</v>
       </c>
       <c r="G10">
-        <v>0.542</v>
+        <v>0.545</v>
       </c>
       <c r="H10">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="I10">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2390,25 +2467,25 @@
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11">
-        <v>100.1</v>
+        <v>112.45</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F11">
-        <v>117.87</v>
+        <v>117.54</v>
       </c>
       <c r="G11">
-        <v>0.542</v>
+        <v>0.455</v>
       </c>
       <c r="H11">
-        <v>-0.8</v>
+        <v>-1.5</v>
       </c>
       <c r="I11">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2423,31 +2500,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2455,28 +2532,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>143.59</v>
+        <v>138.8266666666667</v>
       </c>
       <c r="E2">
-        <v>287.18</v>
+        <v>416.48</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2484,231 +2561,231 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C3">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
-        <v>150.25</v>
+        <v>141.6</v>
       </c>
       <c r="E3">
-        <v>300.5</v>
+        <v>424.8</v>
       </c>
       <c r="F3">
-        <v>99.8</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D4">
-        <v>118.83</v>
+        <v>125.72</v>
       </c>
       <c r="E4">
-        <v>237.66</v>
+        <v>377.16</v>
       </c>
       <c r="F4">
-        <v>96.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5">
-        <v>127.29</v>
+        <v>119.4666666666667</v>
       </c>
       <c r="E5">
-        <v>254.58</v>
+        <v>358.4</v>
       </c>
       <c r="F5">
-        <v>95.19999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D6">
-        <v>126.29</v>
+        <v>119.4866666666667</v>
       </c>
       <c r="E6">
-        <v>252.58</v>
+        <v>358.46</v>
       </c>
       <c r="F6">
-        <v>90.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G6">
         <v>0.2</v>
       </c>
       <c r="H6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D7">
-        <v>111.79</v>
+        <v>112.4466666666667</v>
       </c>
       <c r="E7">
-        <v>223.58</v>
+        <v>337.34</v>
       </c>
       <c r="F7">
-        <v>47.5</v>
+        <v>42.9</v>
       </c>
       <c r="G7">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="H7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D8">
-        <v>106.72</v>
+        <v>113.68</v>
       </c>
       <c r="E8">
-        <v>213.44</v>
+        <v>341.04</v>
       </c>
       <c r="F8">
-        <v>31.4</v>
+        <v>34.2</v>
       </c>
       <c r="G8">
-        <v>6.7</v>
+        <v>5.1</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="I8" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D9">
-        <v>106.28</v>
+        <v>110.7066666666667</v>
       </c>
       <c r="E9">
-        <v>212.56</v>
+        <v>332.12</v>
       </c>
       <c r="F9">
-        <v>27.3</v>
+        <v>26.3</v>
       </c>
       <c r="G9">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I9" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D10">
-        <v>100.1</v>
+        <v>108.9</v>
       </c>
       <c r="E10">
-        <v>200.2</v>
+        <v>326.7</v>
       </c>
       <c r="F10">
-        <v>7.3</v>
+        <v>24.9</v>
       </c>
       <c r="G10">
-        <v>35.7</v>
+        <v>10.5</v>
       </c>
       <c r="H10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2716,28 +2793,28 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>98.92</v>
+        <v>101.9333333333333</v>
       </c>
       <c r="E11">
-        <v>197.84</v>
+        <v>305.8</v>
       </c>
       <c r="F11">
-        <v>4.399999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="G11">
-        <v>47.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="H11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I11" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2752,19 +2829,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2775,16 +2852,16 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2792,19 +2869,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -2812,19 +2889,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2832,19 +2909,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2855,16 +2932,16 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2875,7 +2952,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -2884,7 +2961,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2895,16 +2972,16 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2912,7 +2989,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
         <v>48</v>
@@ -2921,10 +2998,10 @@
         <v>-2</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2932,19 +3009,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2952,19 +3029,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D11">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -2974,21 +3051,24 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>95</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -2998,53 +3078,65 @@
       <c r="C2">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="D2">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -3054,11 +3146,14 @@
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
@@ -3068,11 +3163,14 @@
       <c r="C7">
         <v>0</v>
       </c>
-      <c r="D7" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -3082,50 +3180,62 @@
       <c r="C8">
         <v>-1</v>
       </c>
-      <c r="D8" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="D8">
+        <v>-2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>-4</v>
+      </c>
+      <c r="C9">
+        <v>-6</v>
+      </c>
+      <c r="D9">
+        <v>-2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B9">
+      <c r="B10">
         <v>-2</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <v>-2</v>
       </c>
-      <c r="D9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="D10">
+        <v>-7</v>
+      </c>
+      <c r="E10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>-6</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>-5</v>
       </c>
-      <c r="D10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11">
-        <v>-4</v>
-      </c>
-      <c r="C11">
-        <v>-6</v>
-      </c>
-      <c r="D11" t="s">
-        <v>87</v>
+      <c r="D11">
+        <v>-7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Fantasy 2026 2026.xlsx
+++ b/data/leagues/Fantasy 2026 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="104">
   <si>
     <t>Fumbledore</t>
   </si>
@@ -55,16 +55,19 @@
     <t>Amanda's Awesome Team</t>
   </si>
   <si>
-    <t>2-1-0</t>
-  </si>
-  <si>
-    <t>1-2-0</t>
-  </si>
-  <si>
-    <t>3-0-0</t>
-  </si>
-  <si>
-    <t>0-3-0</t>
+    <t>3-1-0</t>
+  </si>
+  <si>
+    <t>2-2-0</t>
+  </si>
+  <si>
+    <t>4-0-0</t>
+  </si>
+  <si>
+    <t>1-3-0</t>
+  </si>
+  <si>
+    <t>0-4-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -130,6 +133,9 @@
     <t>Week_4</t>
   </si>
   <si>
+    <t>Week_5</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -154,30 +160,30 @@
     <t>Hilary Manion</t>
   </si>
   <si>
+    <t>chloe melvin</t>
+  </si>
+  <si>
+    <t>Marianne Schulmeister</t>
+  </si>
+  <si>
+    <t>kaitlin hahn</t>
+  </si>
+  <si>
+    <t>ashley Lavery</t>
+  </si>
+  <si>
+    <t>Michele Schul</t>
+  </si>
+  <si>
+    <t>Amanda Pasquale</t>
+  </si>
+  <si>
+    <t>Madison Dietz</t>
+  </si>
+  <si>
     <t>Meghan Bishop</t>
   </si>
   <si>
-    <t>Michele Schul</t>
-  </si>
-  <si>
-    <t>kaitlin hahn</t>
-  </si>
-  <si>
-    <t>chloe melvin</t>
-  </si>
-  <si>
-    <t>ashley Lavery</t>
-  </si>
-  <si>
-    <t>Marianne Schulmeister</t>
-  </si>
-  <si>
-    <t>Amanda Pasquale</t>
-  </si>
-  <si>
-    <t>Madison Dietz</t>
-  </si>
-  <si>
     <t>Shannon Finegan</t>
   </si>
   <si>
@@ -205,46 +211,46 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
   </si>
   <si>
     <t>11.2-2.7-0.1</t>
   </si>
   <si>
-    <t>10.0-3.9-0.1</t>
-  </si>
-  <si>
-    <t>8.7-5.2-0.1</t>
-  </si>
-  <si>
-    <t>7.9-5.9-0.1</t>
-  </si>
-  <si>
-    <t>7.5-6.4-0.1</t>
-  </si>
-  <si>
-    <t>5.8-8.0-0.1</t>
-  </si>
-  <si>
-    <t>5.4-8.5-0.1</t>
-  </si>
-  <si>
-    <t>5.2-8.7-0.1</t>
-  </si>
-  <si>
-    <t>5.0-8.8-0.1</t>
-  </si>
-  <si>
-    <t>2.8-11.1-0.1</t>
+    <t>9.7-4.2-0.1</t>
+  </si>
+  <si>
+    <t>9.4-4.5-0.1</t>
+  </si>
+  <si>
+    <t>6.8-7.1-0.1</t>
+  </si>
+  <si>
+    <t>6.4-7.4-0.1</t>
+  </si>
+  <si>
+    <t>6.0-7.9-0.1</t>
+  </si>
+  <si>
+    <t>5.8-8.1-0.1</t>
+  </si>
+  <si>
+    <t>5.3-8.6-0.1</t>
+  </si>
+  <si>
+    <t>4.6-9.2-0.1</t>
+  </si>
+  <si>
+    <t>4.2-9.7-0.1</t>
   </si>
   <si>
     <t>11-3</t>
@@ -253,12 +259,6 @@
     <t>10-4</t>
   </si>
   <si>
-    <t>9-5</t>
-  </si>
-  <si>
-    <t>8-6</t>
-  </si>
-  <si>
     <t>7-7</t>
   </si>
   <si>
@@ -268,7 +268,7 @@
     <t>5-9</t>
   </si>
   <si>
-    <t>2-12</t>
+    <t>4-10</t>
   </si>
   <si>
     <t>Owners</t>
@@ -280,28 +280,28 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑1</t>
-  </si>
-  <si>
-    <t>↑6</t>
+    <t>↑7</t>
+  </si>
+  <si>
+    <t>↑9</t>
+  </si>
+  <si>
+    <t>↓2</t>
+  </si>
+  <si>
+    <t>↑2</t>
   </si>
   <si>
     <t>↓3</t>
   </si>
   <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↑4</t>
+    <t>↑5</t>
   </si>
   <si>
     <t>↓5</t>
   </si>
   <si>
-    <t>↓2</t>
+    <t>↓6</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>Week 3</t>
+  </si>
+  <si>
+    <t>Week 4</t>
   </si>
   <si>
     <t>Week</t>
@@ -732,13 +735,13 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -747,13 +750,13 @@
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K2" t="s">
         <v>10</v>
@@ -767,13 +770,13 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
         <v>10</v>
@@ -782,13 +785,13 @@
         <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K3" t="s">
         <v>11</v>
@@ -820,7 +823,7 @@
         <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J4" t="s">
         <v>11</v>
@@ -834,34 +837,34 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -869,31 +872,31 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
         <v>10</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6" t="s">
         <v>10</v>
@@ -907,7 +910,7 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -922,10 +925,10 @@
         <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7" t="s">
         <v>11</v>
@@ -977,7 +980,7 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -992,10 +995,10 @@
         <v>11</v>
       </c>
       <c r="H9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J9" t="s">
         <v>11</v>
@@ -1009,34 +1012,34 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
       </c>
       <c r="H10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1047,13 +1050,13 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
         <v>10</v>
@@ -1062,10 +1065,10 @@
         <v>12</v>
       </c>
       <c r="H11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J11" t="s">
         <v>10</v>
@@ -1081,30 +1084,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1112,25 +1115,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>2</v>
-      </c>
       <c r="E2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>-5</v>
+        <v>14</v>
       </c>
       <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
         <v>6</v>
-      </c>
-      <c r="H2" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1141,22 +1144,22 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>-5</v>
+      </c>
+      <c r="G3">
         <v>6</v>
       </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>-1</v>
-      </c>
-      <c r="F3">
-        <v>-6</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
       <c r="H3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1164,24 +1167,102 @@
         <v>2</v>
       </c>
       <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4">
+        <v>-1</v>
+      </c>
+      <c r="F4">
+        <v>-6</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>-2</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>-10</v>
+      </c>
+      <c r="F6">
+        <v>-7</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D7" t="s">
         <v>4</v>
       </c>
-      <c r="E4">
+      <c r="E7">
         <v>1</v>
       </c>
-      <c r="F4">
+      <c r="F7">
         <v>0</v>
       </c>
-      <c r="G4">
+      <c r="G7">
         <v>1</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H7" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1197,13 +1278,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1214,10 +1295,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1228,10 +1309,10 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1239,13 +1320,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1256,10 +1337,10 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1267,10 +1348,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
@@ -1281,13 +1362,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1295,13 +1376,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1309,13 +1390,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1326,10 +1407,10 @@
         <v>4</v>
       </c>
       <c r="C10">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1340,7 +1421,7 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -1358,16 +1439,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1378,10 +1459,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>-0.6000000000000001</v>
+        <v>-1</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
@@ -1392,13 +1473,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -1409,13 +1490,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="D4">
-        <v>-0.1000000000000001</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1426,16 +1507,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="D5">
-        <v>-0.2</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1443,16 +1524,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="D6">
-        <v>-0.6000000000000001</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1463,13 +1544,13 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="D7">
-        <v>0.3999999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1477,16 +1558,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="D8">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1494,13 +1575,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="D9">
-        <v>0.1000000000000001</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -1511,16 +1592,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="D10">
-        <v>0.1000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1531,10 +1612,10 @@
         <v>5</v>
       </c>
       <c r="C11">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="D11">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -1552,40 +1633,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1593,22 +1674,22 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>61.4</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="C2">
-        <v>29.6</v>
+        <v>22.2</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="E2">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="F2">
         <v>0.5</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1617,13 +1698,13 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1631,37 +1712,37 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <v>32</v>
+        <v>21.9</v>
       </c>
       <c r="C3">
-        <v>38.2</v>
+        <v>39.2</v>
       </c>
       <c r="D3">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="F3">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="G3">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="H3">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="I3">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>99.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1669,75 +1750,75 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>3.9</v>
+        <v>9.5</v>
       </c>
       <c r="C4">
-        <v>18.5</v>
+        <v>32.2</v>
       </c>
       <c r="D4">
-        <v>34.9</v>
+        <v>41.3</v>
       </c>
       <c r="E4">
-        <v>20.4</v>
+        <v>11.7</v>
       </c>
       <c r="F4">
-        <v>13.4</v>
+        <v>3.2</v>
       </c>
       <c r="G4">
-        <v>5.5</v>
+        <v>1.4</v>
       </c>
       <c r="H4">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="I4">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J4">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>0.1</v>
       </c>
       <c r="L4">
-        <v>96.59999999999999</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="C5">
-        <v>7.7</v>
+        <v>3.4</v>
       </c>
       <c r="D5">
-        <v>18.7</v>
+        <v>8.4</v>
       </c>
       <c r="E5">
-        <v>28.1</v>
+        <v>28.3</v>
       </c>
       <c r="F5">
-        <v>21.6</v>
+        <v>19.2</v>
       </c>
       <c r="G5">
-        <v>11.8</v>
+        <v>15.2</v>
       </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>10.3</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="J5">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>89.40000000000001</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1745,37 +1826,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="C6">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="D6">
-        <v>14.1</v>
+        <v>4.9</v>
       </c>
       <c r="E6">
-        <v>23.8</v>
+        <v>20.4</v>
       </c>
       <c r="F6">
-        <v>25.2</v>
+        <v>19.2</v>
       </c>
       <c r="G6">
-        <v>15.8</v>
+        <v>18.2</v>
       </c>
       <c r="H6">
-        <v>10.1</v>
+        <v>16.9</v>
       </c>
       <c r="I6">
-        <v>3.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="K6">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>84.59999999999999</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1783,156 +1864,156 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="D7">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="E7">
-        <v>6.8</v>
+        <v>14.1</v>
       </c>
       <c r="F7">
+        <v>20.3</v>
+      </c>
+      <c r="G7">
+        <v>17.9</v>
+      </c>
+      <c r="H7">
+        <v>15.1</v>
+      </c>
+      <c r="I7">
         <v>12.7</v>
       </c>
-      <c r="G7">
-        <v>20</v>
-      </c>
-      <c r="H7">
-        <v>21.9</v>
-      </c>
-      <c r="I7">
-        <v>17.9</v>
-      </c>
       <c r="J7">
-        <v>12.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K7">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="L7">
-        <v>42.9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B8">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>0.3</v>
       </c>
       <c r="D8">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="E8">
-        <v>5.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F8">
-        <v>9.5</v>
+        <v>11.4</v>
       </c>
       <c r="G8">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="H8">
-        <v>21</v>
+        <v>16.9</v>
       </c>
       <c r="I8">
-        <v>23.2</v>
+        <v>19.3</v>
       </c>
       <c r="J8">
-        <v>16.5</v>
+        <v>12.3</v>
       </c>
       <c r="K8">
-        <v>5.1</v>
+        <v>10.1</v>
       </c>
       <c r="L8">
-        <v>34.2</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D9">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="E9">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="F9">
-        <v>7.9</v>
+        <v>13.6</v>
       </c>
       <c r="G9">
-        <v>13.2</v>
+        <v>14.2</v>
       </c>
       <c r="H9">
-        <v>19.1</v>
+        <v>17</v>
       </c>
       <c r="I9">
-        <v>22.7</v>
+        <v>17.5</v>
       </c>
       <c r="J9">
-        <v>23</v>
+        <v>16.7</v>
       </c>
       <c r="K9">
-        <v>8.9</v>
+        <v>12.9</v>
       </c>
       <c r="L9">
-        <v>26.3</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="D10">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="E10">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="F10">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
       <c r="G10">
-        <v>13.7</v>
+        <v>8.1</v>
       </c>
       <c r="H10">
-        <v>16.4</v>
+        <v>13.5</v>
       </c>
       <c r="I10">
-        <v>22.4</v>
+        <v>17.9</v>
       </c>
       <c r="J10">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="K10">
-        <v>10.5</v>
+        <v>26.2</v>
       </c>
       <c r="L10">
-        <v>24.9</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1941,31 +2022,31 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="F11">
-        <v>0.2</v>
+        <v>3.6</v>
       </c>
       <c r="G11">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="H11">
-        <v>2.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I11">
-        <v>6.7</v>
+        <v>14.4</v>
       </c>
       <c r="J11">
-        <v>18.4</v>
+        <v>24.5</v>
       </c>
       <c r="K11">
-        <v>70.59999999999999</v>
+        <v>40.2</v>
       </c>
       <c r="L11">
-        <v>2.1</v>
+        <v>11.2</v>
       </c>
     </row>
   </sheetData>
@@ -1975,24 +2056,27 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>35</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -2003,163 +2087,193 @@
         <v>100</v>
       </c>
       <c r="D2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="E2">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>42.8</v>
+      </c>
+      <c r="C3">
+        <v>96.89999999999999</v>
+      </c>
+      <c r="D3">
+        <v>97.89999999999999</v>
+      </c>
+      <c r="E3">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="F3">
+        <v>99.59999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>100</v>
       </c>
-      <c r="C3">
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
         <v>99.8</v>
       </c>
-      <c r="D3">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="E3">
-        <v>99.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>43.2</v>
-      </c>
-      <c r="C4">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="D4">
-        <v>97.09999999999999</v>
-      </c>
       <c r="E4">
-        <v>96.89999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="F4">
+        <v>99.40000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>67</v>
+        <v>85.8</v>
       </c>
       <c r="C5">
-        <v>95.39999999999999</v>
+        <v>28.3</v>
       </c>
       <c r="D5">
-        <v>90.60000000000001</v>
+        <v>24.2</v>
       </c>
       <c r="E5">
-        <v>90.40000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="F5">
+        <v>74.59999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>95.5</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="C6">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="D6">
-        <v>84.39999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="E6">
-        <v>83.59999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>60.09999999999999</v>
+      </c>
+      <c r="F6">
+        <v>64.60000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B7">
-        <v>50</v>
+        <v>52.1</v>
       </c>
       <c r="C7">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>44.9</v>
+        <v>44.1</v>
       </c>
       <c r="E7">
-        <v>42.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>58.3</v>
+      </c>
+      <c r="F7">
+        <v>55.90000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8">
+        <v>66.7</v>
+      </c>
+      <c r="C8">
+        <v>95.5</v>
+      </c>
+      <c r="D8">
+        <v>91.7</v>
+      </c>
+      <c r="E8">
+        <v>43.8</v>
+      </c>
+      <c r="F8">
+        <v>39.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>0.3</v>
+      </c>
+      <c r="C9">
+        <v>29.8</v>
+      </c>
+      <c r="D9">
+        <v>21.4</v>
+      </c>
+      <c r="E9">
+        <v>31.4</v>
+      </c>
+      <c r="F9">
+        <v>35.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>2.4</v>
+      </c>
+      <c r="C10">
+        <v>2.5</v>
+      </c>
+      <c r="D10">
+        <v>2.2</v>
+      </c>
+      <c r="E10">
+        <v>21.6</v>
+      </c>
+      <c r="F10">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8">
-        <v>55.50000000000001</v>
-      </c>
-      <c r="C8">
-        <v>90.2</v>
-      </c>
-      <c r="D8">
-        <v>32.8</v>
-      </c>
-      <c r="E8">
-        <v>34.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9">
-        <v>85.5</v>
-      </c>
-      <c r="C9">
-        <v>31.5</v>
-      </c>
-      <c r="D9">
-        <v>26.2</v>
-      </c>
-      <c r="E9">
-        <v>29.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>0.2</v>
-      </c>
-      <c r="C10">
-        <v>28.4</v>
-      </c>
-      <c r="D10">
-        <v>22.2</v>
-      </c>
-      <c r="E10">
-        <v>20.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="B11">
-        <v>3.1</v>
+        <v>52.8</v>
       </c>
       <c r="C11">
-        <v>2.9</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>34.4</v>
       </c>
       <c r="E11">
-        <v>2.3</v>
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>10.6</v>
       </c>
     </row>
   </sheetData>
@@ -2174,28 +2288,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2206,25 +2320,25 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>101.93</v>
+        <v>110.38</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
       </c>
       <c r="F2">
-        <v>120.25</v>
+        <v>120.47</v>
       </c>
       <c r="G2">
-        <v>0.545</v>
+        <v>0.5</v>
       </c>
       <c r="H2">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="I2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2232,28 +2346,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3">
-        <v>110.71</v>
+        <v>116.1</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3">
-        <v>119.45</v>
+        <v>119.88</v>
       </c>
       <c r="G3">
-        <v>0.515</v>
+        <v>0.5</v>
       </c>
       <c r="H3">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2261,28 +2375,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D4">
-        <v>125.72</v>
+        <v>110.67</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>117.24</v>
+        <v>119.98</v>
       </c>
       <c r="G4">
-        <v>0.455</v>
+        <v>0.475</v>
       </c>
       <c r="H4">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I4">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2293,25 +2407,25 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5">
-        <v>141.6</v>
+        <v>135.59</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5">
-        <v>119.04</v>
+        <v>119.8</v>
       </c>
       <c r="G5">
-        <v>0.545</v>
+        <v>0.525</v>
       </c>
       <c r="H5">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2319,28 +2433,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D6">
-        <v>119.49</v>
+        <v>108.14</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F6">
-        <v>120.51</v>
+        <v>121.7</v>
       </c>
       <c r="G6">
-        <v>0.485</v>
+        <v>0.55</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2348,28 +2462,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>113.68</v>
+        <v>128.42</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>122.15</v>
+        <v>117.64</v>
       </c>
       <c r="G7">
-        <v>0.576</v>
+        <v>0.45</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2377,28 +2491,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>119.47</v>
+        <v>136.92</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>116.74</v>
+        <v>119.53</v>
       </c>
       <c r="G8">
-        <v>0.424</v>
+        <v>0.475</v>
       </c>
       <c r="H8">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2406,28 +2520,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9">
-        <v>138.83</v>
+        <v>113.75</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>119.02</v>
+        <v>119.36</v>
       </c>
       <c r="G9">
-        <v>0.455</v>
+        <v>0.525</v>
       </c>
       <c r="H9">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="I9">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2435,28 +2549,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10">
-        <v>108.9</v>
+        <v>118.26</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
       </c>
       <c r="F10">
-        <v>120.82</v>
+        <v>119.45</v>
       </c>
       <c r="G10">
-        <v>0.545</v>
+        <v>0.5</v>
       </c>
       <c r="H10">
-        <v>-0.8</v>
+        <v>-1.4</v>
       </c>
       <c r="I10">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2467,25 +2581,25 @@
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D11">
-        <v>112.45</v>
+        <v>118.45</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>117.54</v>
+        <v>118.86</v>
       </c>
       <c r="G11">
-        <v>0.455</v>
+        <v>0.5</v>
       </c>
       <c r="H11">
-        <v>-1.5</v>
+        <v>-2.5</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2500,31 +2614,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2532,28 +2646,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>138.8266666666667</v>
+        <v>136.92</v>
       </c>
       <c r="E2">
-        <v>416.48</v>
+        <v>547.6800000000001</v>
       </c>
       <c r="F2">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2561,28 +2675,28 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D3">
-        <v>141.6</v>
+        <v>135.585</v>
       </c>
       <c r="E3">
-        <v>424.8</v>
+        <v>542.34</v>
       </c>
       <c r="F3">
-        <v>99.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2590,57 +2704,57 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C4">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="D4">
-        <v>125.72</v>
+        <v>128.42</v>
       </c>
       <c r="E4">
-        <v>377.16</v>
+        <v>513.6799999999999</v>
       </c>
       <c r="F4">
-        <v>96.59999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="G4">
         <v>0.1</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C5">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D5">
-        <v>119.4666666666667</v>
+        <v>118.26</v>
       </c>
       <c r="E5">
-        <v>358.4</v>
+        <v>473.04</v>
       </c>
       <c r="F5">
-        <v>89.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2648,25 +2762,25 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C6">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>119.4866666666667</v>
+        <v>116.1</v>
       </c>
       <c r="E6">
-        <v>358.46</v>
+        <v>464.4</v>
       </c>
       <c r="F6">
-        <v>84.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="G6">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I6" t="s">
         <v>78</v>
@@ -2677,25 +2791,25 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C7">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D7">
-        <v>112.4466666666667</v>
+        <v>118.45</v>
       </c>
       <c r="E7">
-        <v>337.34</v>
+        <v>473.8</v>
       </c>
       <c r="F7">
-        <v>42.9</v>
+        <v>56.99999999999999</v>
       </c>
       <c r="G7">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="H7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I7" t="s">
         <v>79</v>
@@ -2703,57 +2817,57 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C8">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>113.68</v>
+        <v>110.67</v>
       </c>
       <c r="E8">
-        <v>341.04</v>
+        <v>442.6800000000001</v>
       </c>
       <c r="F8">
-        <v>34.2</v>
+        <v>41.4</v>
       </c>
       <c r="G8">
-        <v>5.1</v>
+        <v>10.1</v>
       </c>
       <c r="H8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C9">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D9">
-        <v>110.7066666666667</v>
+        <v>113.75</v>
       </c>
       <c r="E9">
-        <v>332.12</v>
+        <v>455</v>
       </c>
       <c r="F9">
-        <v>26.3</v>
+        <v>35.9</v>
       </c>
       <c r="G9">
-        <v>8.9</v>
+        <v>12.9</v>
       </c>
       <c r="H9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I9" t="s">
         <v>80</v>
@@ -2761,28 +2875,28 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C10">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="D10">
-        <v>108.9</v>
+        <v>110.38</v>
       </c>
       <c r="E10">
-        <v>326.7</v>
+        <v>441.52</v>
       </c>
       <c r="F10">
-        <v>24.9</v>
+        <v>16.7</v>
       </c>
       <c r="G10">
-        <v>10.5</v>
+        <v>26.2</v>
       </c>
       <c r="H10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I10" t="s">
         <v>80</v>
@@ -2790,28 +2904,28 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D11">
-        <v>101.9333333333333</v>
+        <v>108.14</v>
       </c>
       <c r="E11">
-        <v>305.8</v>
+        <v>432.5599999999999</v>
       </c>
       <c r="F11">
-        <v>2.1</v>
+        <v>11.2</v>
       </c>
       <c r="G11">
-        <v>70.59999999999999</v>
+        <v>40.2</v>
       </c>
       <c r="H11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I11" t="s">
         <v>81</v>
@@ -2829,7 +2943,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>82</v>
@@ -2838,7 +2952,7 @@
         <v>83</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>84</v>
@@ -2849,16 +2963,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
         <v>85</v>
@@ -2869,10 +2983,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3">
         <v>7</v>
@@ -2889,19 +3003,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -2909,19 +3023,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -2929,19 +3043,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2949,19 +3063,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2969,19 +3083,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2989,19 +3103,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D9">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3009,16 +3123,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D10">
         <v>-7</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>91</v>
@@ -3029,19 +3143,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C11" t="s">
         <v>44</v>
       </c>
       <c r="D11">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F11" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -3051,10 +3165,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
         <v>93</v>
       </c>
@@ -3065,177 +3179,210 @@
         <v>95</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>-1</v>
+      </c>
+      <c r="D3">
+        <v>-2</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2">
+      <c r="B4">
         <v>5</v>
       </c>
-      <c r="C2">
+      <c r="C4">
         <v>7</v>
       </c>
-      <c r="D2">
+      <c r="D4">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3">
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>-1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="F5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6">
         <v>1</v>
-      </c>
-      <c r="D3">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>-1</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>-1</v>
+      </c>
+      <c r="F6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>-6</v>
+      </c>
+      <c r="C7">
+        <v>-5</v>
+      </c>
+      <c r="D7">
+        <v>-7</v>
+      </c>
+      <c r="E7">
+        <v>-2</v>
+      </c>
+      <c r="F7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>-4</v>
+      </c>
+      <c r="F8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9">
         <v>0</v>
       </c>
-      <c r="E6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
+      <c r="C9">
         <v>0</v>
       </c>
-      <c r="C7">
+      <c r="D9">
         <v>0</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8">
-        <v>-1</v>
-      </c>
-      <c r="D8">
+      <c r="E9">
+        <v>-6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>-4</v>
+      </c>
+      <c r="C10">
+        <v>-6</v>
+      </c>
+      <c r="D10">
         <v>-2</v>
       </c>
-      <c r="E8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>-4</v>
-      </c>
-      <c r="C9">
-        <v>-6</v>
-      </c>
-      <c r="D9">
+      <c r="E10">
+        <v>-7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11">
         <v>-2</v>
       </c>
-      <c r="E9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10">
+      <c r="C11">
         <v>-2</v>
-      </c>
-      <c r="C10">
-        <v>-2</v>
-      </c>
-      <c r="D10">
-        <v>-7</v>
-      </c>
-      <c r="E10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11">
-        <v>-6</v>
-      </c>
-      <c r="C11">
-        <v>-5</v>
       </c>
       <c r="D11">
         <v>-7</v>
       </c>
-      <c r="E11" t="s">
-        <v>92</v>
+      <c r="E11">
+        <v>-10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Fantasy 2026 2026.xlsx
+++ b/data/leagues/Fantasy 2026 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="109">
   <si>
     <t>Fumbledore</t>
   </si>
@@ -55,19 +55,22 @@
     <t>Amanda's Awesome Team</t>
   </si>
   <si>
-    <t>3-1-0</t>
-  </si>
-  <si>
-    <t>2-2-0</t>
-  </si>
-  <si>
-    <t>4-0-0</t>
-  </si>
-  <si>
-    <t>1-3-0</t>
-  </si>
-  <si>
-    <t>0-4-0</t>
+    <t>4-1-0</t>
+  </si>
+  <si>
+    <t>3-2-0</t>
+  </si>
+  <si>
+    <t>2-3-0</t>
+  </si>
+  <si>
+    <t>1-4-0</t>
+  </si>
+  <si>
+    <t>5-0-0</t>
+  </si>
+  <si>
+    <t>0-5-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -136,6 +139,9 @@
     <t>Week_5</t>
   </si>
   <si>
+    <t>Week_6</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -157,36 +163,36 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Michele Schul</t>
+  </si>
+  <si>
+    <t>ashley Lavery</t>
+  </si>
+  <si>
     <t>Hilary Manion</t>
   </si>
   <si>
+    <t>kaitlin hahn</t>
+  </si>
+  <si>
+    <t>Marianne Schulmeister</t>
+  </si>
+  <si>
     <t>chloe melvin</t>
   </si>
   <si>
-    <t>Marianne Schulmeister</t>
-  </si>
-  <si>
-    <t>kaitlin hahn</t>
-  </si>
-  <si>
-    <t>ashley Lavery</t>
-  </si>
-  <si>
-    <t>Michele Schul</t>
-  </si>
-  <si>
     <t>Amanda Pasquale</t>
   </si>
   <si>
     <t>Madison Dietz</t>
   </si>
   <si>
+    <t>Shannon Finegan</t>
+  </si>
+  <si>
     <t>Meghan Bishop</t>
   </si>
   <si>
-    <t>Shannon Finegan</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -211,58 +217,58 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>11.2-2.7-0.1</t>
-  </si>
-  <si>
-    <t>9.7-4.2-0.1</t>
-  </si>
-  <si>
-    <t>9.4-4.5-0.1</t>
-  </si>
-  <si>
-    <t>6.8-7.1-0.1</t>
-  </si>
-  <si>
-    <t>6.4-7.4-0.1</t>
-  </si>
-  <si>
-    <t>6.0-7.9-0.1</t>
-  </si>
-  <si>
-    <t>5.8-8.1-0.1</t>
-  </si>
-  <si>
-    <t>5.3-8.6-0.1</t>
-  </si>
-  <si>
-    <t>4.6-9.2-0.1</t>
-  </si>
-  <si>
-    <t>4.2-9.7-0.1</t>
-  </si>
-  <si>
-    <t>11-3</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>9.8-4.1-0.1</t>
+  </si>
+  <si>
+    <t>9.1-4.8-0.1</t>
+  </si>
+  <si>
+    <t>8.5-5.4-0.1</t>
+  </si>
+  <si>
+    <t>7.4-6.5-0.1</t>
+  </si>
+  <si>
+    <t>7.3-6.6-0.1</t>
+  </si>
+  <si>
+    <t>6.7-7.2-0.1</t>
+  </si>
+  <si>
+    <t>5.9-8.0-0.1</t>
+  </si>
+  <si>
+    <t>5.1-8.8-0.1</t>
+  </si>
+  <si>
+    <t>4.9-9.0-0.1</t>
+  </si>
+  <si>
+    <t>4.7-9.2-0.1</t>
   </si>
   <si>
     <t>10-4</t>
   </si>
   <si>
+    <t>9-5</t>
+  </si>
+  <si>
     <t>7-7</t>
   </si>
   <si>
-    <t>6-8</t>
+    <t>8-6</t>
   </si>
   <si>
     <t>5-9</t>
@@ -280,28 +286,34 @@
     <t>Change From Last Week</t>
   </si>
   <si>
+    <t>↑10</t>
+  </si>
+  <si>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↓5</t>
+  </si>
+  <si>
     <t>↑7</t>
   </si>
   <si>
-    <t>↑9</t>
-  </si>
-  <si>
-    <t>↓2</t>
+    <t>↑5</t>
+  </si>
+  <si>
+    <t>↓3</t>
   </si>
   <si>
     <t>↑2</t>
   </si>
   <si>
-    <t>↓3</t>
-  </si>
-  <si>
-    <t>↑5</t>
-  </si>
-  <si>
-    <t>↓5</t>
-  </si>
-  <si>
-    <t>↓6</t>
+    <t>↓7</t>
+  </si>
+  <si>
+    <t>↓10</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -314,6 +326,9 @@
   </si>
   <si>
     <t>Week 4</t>
+  </si>
+  <si>
+    <t>Week 5</t>
   </si>
   <si>
     <t>Week</t>
@@ -735,7 +750,7 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -744,19 +759,19 @@
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K2" t="s">
         <v>10</v>
@@ -779,7 +794,7 @@
         <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -788,13 +803,13 @@
         <v>13</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -802,34 +817,34 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
       <c r="G4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -840,7 +855,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -849,19 +864,19 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" t="s">
         <v>13</v>
       </c>
-      <c r="I5" t="s">
-        <v>14</v>
-      </c>
       <c r="J5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K5" t="s">
         <v>11</v>
@@ -884,16 +899,16 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>10</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J6" t="s">
         <v>11</v>
@@ -919,22 +934,22 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" t="s">
         <v>13</v>
       </c>
-      <c r="H7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" t="s">
-        <v>14</v>
-      </c>
       <c r="J7" t="s">
         <v>11</v>
       </c>
       <c r="K7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -945,10 +960,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
@@ -957,13 +972,13 @@
         <v>10</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
       </c>
       <c r="I8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J8" t="s">
         <v>11</v>
@@ -986,13 +1001,13 @@
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H9" t="s">
         <v>13</v>
@@ -1004,7 +1019,7 @@
         <v>11</v>
       </c>
       <c r="K9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1021,25 +1036,25 @@
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H10" t="s">
         <v>13</v>
       </c>
       <c r="I10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1047,34 +1062,34 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
         <v>10</v>
       </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" t="s">
-        <v>12</v>
-      </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" t="s">
         <v>10</v>
       </c>
-      <c r="G11" t="s">
-        <v>12</v>
-      </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J11" t="s">
         <v>10</v>
       </c>
       <c r="K11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1084,30 +1099,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1115,25 +1130,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>-8</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1141,25 +1156,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
       <c r="E3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>-5</v>
+        <v>14</v>
       </c>
       <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3" t="s">
         <v>6</v>
-      </c>
-      <c r="H3" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1167,22 +1182,22 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="F4">
-        <v>-6</v>
+        <v>5</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H4" t="s">
         <v>3</v>
@@ -1193,22 +1208,22 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D5" t="s">
         <v>2</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H5" t="s">
         <v>2</v>
@@ -1219,25 +1234,25 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>-4</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
         <v>5</v>
       </c>
-      <c r="D6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>-10</v>
-      </c>
-      <c r="F6">
-        <v>-7</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
       <c r="H6" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1245,24 +1260,102 @@
         <v>5</v>
       </c>
       <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
         <v>3</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7">
+        <v>-1</v>
+      </c>
+      <c r="F7">
+        <v>-6</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>-2</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+      <c r="H8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>-10</v>
+      </c>
+      <c r="F9">
+        <v>-7</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="D7" t="s">
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
         <v>4</v>
       </c>
-      <c r="E7">
+      <c r="E10">
         <v>1</v>
       </c>
-      <c r="F7">
+      <c r="F10">
         <v>0</v>
       </c>
-      <c r="G7">
+      <c r="G10">
         <v>1</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H10" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1278,13 +1371,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1295,7 +1388,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -1309,7 +1402,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -1323,7 +1416,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
@@ -1334,13 +1427,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C5">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1348,13 +1441,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1362,13 +1455,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1376,13 +1469,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1393,10 +1486,10 @@
         <v>9</v>
       </c>
       <c r="C9">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1404,13 +1497,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1421,10 +1514,10 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="D11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1439,16 +1532,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1459,13 +1552,13 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="D2">
-        <v>-1</v>
+        <v>-0.8999999999999999</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1473,16 +1566,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="D3">
-        <v>-0.2999999999999998</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1493,10 +1586,10 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>-0.6000000000000001</v>
+        <v>-1</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1510,13 +1603,13 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="D5">
-        <v>0.1000000000000001</v>
+        <v>0.7999999999999998</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1524,13 +1617,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="D6">
-        <v>0.1000000000000001</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
@@ -1544,10 +1637,10 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="D7">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -1558,16 +1651,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="D8">
-        <v>0.5</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1575,16 +1668,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>-0.6000000000000001</v>
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1592,13 +1685,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="D10">
-        <v>0.3999999999999999</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
@@ -1609,16 +1702,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="D11">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1633,349 +1726,349 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>67.90000000000001</v>
+        <v>54</v>
       </c>
       <c r="C2">
-        <v>22.2</v>
+        <v>23.1</v>
       </c>
       <c r="D2">
-        <v>8.5</v>
+        <v>12.8</v>
       </c>
       <c r="E2">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="F2">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="G2">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>100</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B3">
-        <v>21.9</v>
+        <v>22.8</v>
       </c>
       <c r="C3">
-        <v>39.2</v>
+        <v>28.8</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>21.7</v>
       </c>
       <c r="E3">
-        <v>6.5</v>
+        <v>12.6</v>
       </c>
       <c r="F3">
-        <v>3.5</v>
+        <v>6.7</v>
       </c>
       <c r="G3">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="H3">
+        <v>2.6</v>
+      </c>
+      <c r="I3">
+        <v>0.6</v>
+      </c>
+      <c r="J3">
         <v>0.4</v>
-      </c>
-      <c r="I3">
-        <v>0.1</v>
-      </c>
-      <c r="J3">
-        <v>0.1</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>99.40000000000001</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4">
-        <v>9.5</v>
+        <v>16.3</v>
       </c>
       <c r="C4">
-        <v>32.2</v>
+        <v>24.8</v>
       </c>
       <c r="D4">
-        <v>41.3</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>11.7</v>
+        <v>13.8</v>
       </c>
       <c r="F4">
-        <v>3.2</v>
+        <v>9.9</v>
       </c>
       <c r="G4">
+        <v>5.8</v>
+      </c>
+      <c r="H4">
+        <v>2.8</v>
+      </c>
+      <c r="I4">
         <v>1.4</v>
       </c>
-      <c r="H4">
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
         <v>0.2</v>
       </c>
-      <c r="I4">
-        <v>0.4</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0.1</v>
-      </c>
       <c r="L4">
-        <v>99.3</v>
+        <v>94.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B5">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="C5">
-        <v>3.4</v>
+        <v>8.5</v>
       </c>
       <c r="D5">
-        <v>8.4</v>
+        <v>12.3</v>
       </c>
       <c r="E5">
-        <v>28.3</v>
+        <v>20.3</v>
       </c>
       <c r="F5">
-        <v>19.2</v>
+        <v>17.6</v>
       </c>
       <c r="G5">
         <v>15.2</v>
       </c>
       <c r="H5">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="I5">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="J5">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="L5">
-        <v>74.8</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="C6">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="D6">
-        <v>4.9</v>
+        <v>13.4</v>
       </c>
       <c r="E6">
-        <v>20.4</v>
+        <v>17.7</v>
       </c>
       <c r="F6">
-        <v>19.2</v>
+        <v>18.2</v>
       </c>
       <c r="G6">
-        <v>18.2</v>
+        <v>17</v>
       </c>
       <c r="H6">
-        <v>16.9</v>
+        <v>10.8</v>
       </c>
       <c r="I6">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6">
-        <v>64.3</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>0.7</v>
+        <v>6.6</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E7">
-        <v>14.1</v>
+        <v>15.3</v>
       </c>
       <c r="F7">
-        <v>20.3</v>
+        <v>18.4</v>
       </c>
       <c r="G7">
-        <v>17.9</v>
+        <v>17</v>
       </c>
       <c r="H7">
-        <v>15.1</v>
+        <v>14.4</v>
       </c>
       <c r="I7">
-        <v>12.7</v>
+        <v>10.1</v>
       </c>
       <c r="J7">
-        <v>9.699999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="K7">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="L7">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="C8">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="D8">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="E8">
-        <v>9.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="F8">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="G8">
-        <v>17.8</v>
+        <v>13.8</v>
       </c>
       <c r="H8">
-        <v>16.9</v>
+        <v>18.5</v>
       </c>
       <c r="I8">
-        <v>19.3</v>
+        <v>18.5</v>
       </c>
       <c r="J8">
-        <v>12.3</v>
+        <v>15</v>
       </c>
       <c r="K8">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>41.4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C9">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D9">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="E9">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="F9">
-        <v>13.6</v>
+        <v>7.4</v>
       </c>
       <c r="G9">
-        <v>14.2</v>
+        <v>10.6</v>
       </c>
       <c r="H9">
-        <v>17</v>
+        <v>15.7</v>
       </c>
       <c r="I9">
-        <v>17.5</v>
+        <v>20.6</v>
       </c>
       <c r="J9">
-        <v>16.7</v>
+        <v>19.6</v>
       </c>
       <c r="K9">
-        <v>12.9</v>
+        <v>19.7</v>
       </c>
       <c r="L9">
-        <v>35.9</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1984,31 +2077,31 @@
         <v>0.4</v>
       </c>
       <c r="D10">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="E10">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="F10">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="G10">
-        <v>8.1</v>
+        <v>9.4</v>
       </c>
       <c r="H10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="I10">
-        <v>17.9</v>
+        <v>18.4</v>
       </c>
       <c r="J10">
-        <v>25.7</v>
+        <v>24.9</v>
       </c>
       <c r="K10">
-        <v>26.2</v>
+        <v>23.7</v>
       </c>
       <c r="L10">
-        <v>16.7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2019,34 +2112,34 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D11">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E11">
         <v>1.5</v>
       </c>
       <c r="F11">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="G11">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="H11">
         <v>9.699999999999999</v>
       </c>
       <c r="I11">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="J11">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="K11">
-        <v>40.2</v>
+        <v>40.9</v>
       </c>
       <c r="L11">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
     </row>
   </sheetData>
@@ -2056,29 +2149,32 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>37</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B2">
         <v>100</v>
@@ -2087,192 +2183,222 @@
         <v>100</v>
       </c>
       <c r="D2">
+        <v>99.8</v>
+      </c>
+      <c r="E2">
+        <v>99.7</v>
+      </c>
+      <c r="F2">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="G2">
+        <v>98.90000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
         <v>100</v>
       </c>
-      <c r="E2">
+      <c r="C3">
         <v>100</v>
       </c>
-      <c r="F2">
+      <c r="D3">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
+      <c r="E3">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="G3">
+        <v>97.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="C4">
+        <v>33.4</v>
+      </c>
+      <c r="D4">
+        <v>24.8</v>
+      </c>
+      <c r="E4">
+        <v>73.7</v>
+      </c>
+      <c r="F4">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="G4">
+        <v>95.09999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>68.5</v>
+      </c>
+      <c r="C5">
+        <v>94.89999999999999</v>
+      </c>
+      <c r="D5">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="E5">
+        <v>43.3</v>
+      </c>
+      <c r="F5">
+        <v>74.5</v>
+      </c>
+      <c r="G5">
+        <v>77.10000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>42.8</v>
-      </c>
-      <c r="C3">
-        <v>96.89999999999999</v>
-      </c>
-      <c r="D3">
-        <v>97.89999999999999</v>
-      </c>
-      <c r="E3">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="F3">
-        <v>99.59999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4">
-        <v>100</v>
-      </c>
-      <c r="C4">
-        <v>100</v>
-      </c>
-      <c r="D4">
-        <v>99.8</v>
-      </c>
-      <c r="E4">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="F4">
-        <v>99.40000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>85.8</v>
-      </c>
-      <c r="C5">
-        <v>28.3</v>
-      </c>
-      <c r="D5">
-        <v>24.2</v>
-      </c>
-      <c r="E5">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="F5">
-        <v>74.59999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
+      <c r="B6">
+        <v>41.4</v>
+      </c>
+      <c r="C6">
+        <v>96.39999999999999</v>
+      </c>
+      <c r="D6">
+        <v>97.7</v>
+      </c>
+      <c r="E6">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="F6">
+        <v>74.8</v>
+      </c>
+      <c r="G6">
+        <v>72.09999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="C6">
-        <v>51.6</v>
-      </c>
-      <c r="D6">
-        <v>84.3</v>
-      </c>
-      <c r="E6">
-        <v>60.09999999999999</v>
-      </c>
-      <c r="F6">
-        <v>64.60000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
+      <c r="B7">
+        <v>95.19999999999999</v>
+      </c>
+      <c r="C7">
+        <v>51.1</v>
+      </c>
+      <c r="D7">
+        <v>84.5</v>
+      </c>
+      <c r="E7">
+        <v>62.8</v>
+      </c>
+      <c r="F7">
+        <v>63.7</v>
+      </c>
+      <c r="G7">
+        <v>65.60000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>2.6</v>
+      </c>
+      <c r="C8">
+        <v>2.4</v>
+      </c>
+      <c r="D8">
+        <v>1.6</v>
+      </c>
+      <c r="E8">
+        <v>20.3</v>
+      </c>
+      <c r="F8">
+        <v>41.3</v>
+      </c>
+      <c r="G8">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7">
-        <v>52.1</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>44.1</v>
-      </c>
-      <c r="E7">
-        <v>58.3</v>
-      </c>
-      <c r="F7">
-        <v>55.90000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>66.7</v>
-      </c>
-      <c r="C8">
-        <v>95.5</v>
-      </c>
-      <c r="D8">
-        <v>91.7</v>
-      </c>
-      <c r="E8">
-        <v>43.8</v>
-      </c>
-      <c r="F8">
-        <v>39.7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
+      <c r="B9">
+        <v>53.5</v>
+      </c>
+      <c r="C9">
+        <v>5.600000000000001</v>
+      </c>
+      <c r="D9">
+        <v>47.4</v>
+      </c>
+      <c r="E9">
+        <v>57.09999999999999</v>
+      </c>
+      <c r="F9">
+        <v>29</v>
+      </c>
+      <c r="G9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B9">
-        <v>0.3</v>
-      </c>
-      <c r="C9">
-        <v>29.8</v>
-      </c>
-      <c r="D9">
-        <v>21.4</v>
-      </c>
-      <c r="E9">
-        <v>31.4</v>
-      </c>
-      <c r="F9">
-        <v>35.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="B10">
-        <v>2.4</v>
+        <v>0.1</v>
       </c>
       <c r="C10">
-        <v>2.5</v>
+        <v>27</v>
       </c>
       <c r="D10">
-        <v>2.2</v>
+        <v>19.6</v>
       </c>
       <c r="E10">
-        <v>21.6</v>
+        <v>35.3</v>
       </c>
       <c r="F10">
-        <v>19.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>18</v>
+      </c>
+      <c r="G10">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B11">
-        <v>52.8</v>
+        <v>51.3</v>
       </c>
       <c r="C11">
-        <v>90.40000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="D11">
-        <v>34.4</v>
+        <v>32.7</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="F11">
+        <v>10.8</v>
+      </c>
+      <c r="G11">
         <v>10.6</v>
       </c>
     </row>
@@ -2288,28 +2414,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2317,28 +2443,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2">
-        <v>110.38</v>
+        <v>119.9</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>120.47</v>
+        <v>122.59</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>0.489</v>
       </c>
       <c r="H2">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2346,28 +2472,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D3">
-        <v>116.1</v>
+        <v>108.89</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>119.88</v>
+        <v>123.81</v>
       </c>
       <c r="G3">
-        <v>0.5</v>
+        <v>0.511</v>
       </c>
       <c r="H3">
         <v>1.2</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2375,28 +2501,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D4">
-        <v>110.67</v>
+        <v>118.08</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4">
-        <v>119.98</v>
+        <v>122.79</v>
       </c>
       <c r="G4">
-        <v>0.475</v>
+        <v>0.511</v>
       </c>
       <c r="H4">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2407,25 +2533,25 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5">
-        <v>135.59</v>
+        <v>134.62</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5">
-        <v>119.8</v>
+        <v>120.95</v>
       </c>
       <c r="G5">
-        <v>0.525</v>
+        <v>0.467</v>
       </c>
       <c r="H5">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2433,28 +2559,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D6">
-        <v>108.14</v>
+        <v>120.88</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>121.7</v>
+        <v>122.48</v>
       </c>
       <c r="G6">
-        <v>0.55</v>
+        <v>0.489</v>
       </c>
       <c r="H6">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2462,28 +2588,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7">
-        <v>128.42</v>
+        <v>124.16</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F7">
-        <v>117.64</v>
+        <v>122.12</v>
       </c>
       <c r="G7">
-        <v>0.45</v>
+        <v>0.511</v>
       </c>
       <c r="H7">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2494,25 +2620,25 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8">
-        <v>136.92</v>
+        <v>128.18</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F8">
-        <v>119.53</v>
+        <v>121.67</v>
       </c>
       <c r="G8">
-        <v>0.475</v>
+        <v>0.467</v>
       </c>
       <c r="H8">
-        <v>-0.8</v>
+        <v>-0.1</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2523,25 +2649,25 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9">
-        <v>113.75</v>
+        <v>116.83</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
       </c>
       <c r="F9">
-        <v>119.36</v>
+        <v>122.93</v>
       </c>
       <c r="G9">
-        <v>0.525</v>
+        <v>0.533</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>-0.6</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2549,28 +2675,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10">
-        <v>118.26</v>
+        <v>119.99</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>119.45</v>
+        <v>122.58</v>
       </c>
       <c r="G10">
-        <v>0.5</v>
+        <v>0.533</v>
       </c>
       <c r="H10">
         <v>-1.4</v>
       </c>
       <c r="I10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2578,28 +2704,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D11">
-        <v>118.45</v>
+        <v>131.67</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F11">
-        <v>118.86</v>
+        <v>121.28</v>
       </c>
       <c r="G11">
-        <v>0.5</v>
+        <v>0.489</v>
       </c>
       <c r="H11">
-        <v>-2.5</v>
+        <v>-1.9</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2614,292 +2740,292 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D2">
-        <v>136.92</v>
+        <v>134.616</v>
       </c>
       <c r="E2">
-        <v>547.6800000000001</v>
+        <v>673.08</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D3">
-        <v>135.585</v>
+        <v>128.18</v>
       </c>
       <c r="E3">
-        <v>542.34</v>
+        <v>640.9000000000001</v>
       </c>
       <c r="F3">
-        <v>99.40000000000001</v>
+        <v>96.39999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C4">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="D4">
-        <v>128.42</v>
+        <v>131.668</v>
       </c>
       <c r="E4">
-        <v>513.6799999999999</v>
+        <v>658.3399999999999</v>
       </c>
       <c r="F4">
-        <v>99.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G4">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D5">
-        <v>118.26</v>
+        <v>120.884</v>
       </c>
       <c r="E5">
-        <v>473.04</v>
+        <v>604.4200000000001</v>
       </c>
       <c r="F5">
-        <v>74.8</v>
+        <v>76.2</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="H5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D6">
-        <v>116.1</v>
+        <v>119.904</v>
       </c>
       <c r="E6">
-        <v>464.4</v>
+        <v>599.52</v>
       </c>
       <c r="F6">
-        <v>64.3</v>
+        <v>74.5</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="D7">
-        <v>118.45</v>
+        <v>124.156</v>
       </c>
       <c r="E7">
-        <v>473.8</v>
+        <v>620.78</v>
       </c>
       <c r="F7">
-        <v>56.99999999999999</v>
+        <v>67</v>
       </c>
       <c r="G7">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="H7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D8">
-        <v>110.67</v>
+        <v>118.076</v>
       </c>
       <c r="E8">
-        <v>442.6800000000001</v>
+        <v>590.38</v>
       </c>
       <c r="F8">
-        <v>41.4</v>
+        <v>39</v>
       </c>
       <c r="G8">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="H8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I8" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C9">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D9">
-        <v>113.75</v>
+        <v>119.988</v>
       </c>
       <c r="E9">
-        <v>455</v>
+        <v>599.9399999999999</v>
       </c>
       <c r="F9">
-        <v>35.9</v>
+        <v>24.4</v>
       </c>
       <c r="G9">
-        <v>12.9</v>
+        <v>19.7</v>
       </c>
       <c r="H9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C10">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D10">
-        <v>110.38</v>
+        <v>116.828</v>
       </c>
       <c r="E10">
-        <v>441.52</v>
+        <v>584.14</v>
       </c>
       <c r="F10">
-        <v>16.7</v>
+        <v>19</v>
       </c>
       <c r="G10">
-        <v>26.2</v>
+        <v>23.7</v>
       </c>
       <c r="H10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2907,28 +3033,28 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C11">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="D11">
-        <v>108.14</v>
+        <v>108.892</v>
       </c>
       <c r="E11">
-        <v>432.5599999999999</v>
+        <v>544.4599999999999</v>
       </c>
       <c r="F11">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="G11">
-        <v>40.2</v>
+        <v>40.9</v>
       </c>
       <c r="H11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2943,19 +3069,19 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -2963,19 +3089,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -2983,19 +3109,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3003,19 +3129,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3023,19 +3149,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3043,19 +3169,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3063,19 +3189,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>-2</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3083,19 +3209,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8">
         <v>-4</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3103,19 +3229,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D9">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3123,19 +3249,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3143,19 +3269,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D11">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3165,224 +3291,257 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>101</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>-1</v>
+      </c>
+      <c r="D2">
+        <v>-2</v>
+      </c>
+      <c r="E2">
         <v>7</v>
       </c>
-      <c r="B2">
+      <c r="F2">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C2">
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="D3">
         <v>7</v>
       </c>
-      <c r="E2">
+      <c r="E3">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
+      <c r="F3">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>-1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
         <v>6</v>
       </c>
-      <c r="B3">
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3">
-        <v>-1</v>
-      </c>
-      <c r="D3">
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>-6</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>-4</v>
+      </c>
+      <c r="C7">
+        <v>-6</v>
+      </c>
+      <c r="D7">
         <v>-2</v>
       </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>7</v>
-      </c>
-      <c r="D4">
-        <v>8</v>
-      </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>-1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
+      <c r="E7">
+        <v>-7</v>
+      </c>
+      <c r="F7">
+        <v>-2</v>
+      </c>
+      <c r="G7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>-1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>-6</v>
-      </c>
-      <c r="C7">
-        <v>-5</v>
-      </c>
-      <c r="D7">
-        <v>-7</v>
-      </c>
-      <c r="E7">
-        <v>-2</v>
-      </c>
-      <c r="F7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>-1</v>
+      </c>
+      <c r="F8">
+        <v>-4</v>
+      </c>
+      <c r="G8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>-2</v>
+      </c>
+      <c r="C9">
+        <v>-2</v>
+      </c>
+      <c r="D9">
+        <v>-7</v>
+      </c>
+      <c r="E9">
+        <v>-10</v>
+      </c>
+      <c r="F9">
+        <v>-8</v>
+      </c>
+      <c r="G9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
         <v>4</v>
       </c>
-      <c r="D8">
+      <c r="D10">
         <v>1</v>
       </c>
-      <c r="E8">
+      <c r="E10">
         <v>-4</v>
       </c>
-      <c r="F8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
+      <c r="F10">
+        <v>-11</v>
+      </c>
+      <c r="G10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11">
         <v>-6</v>
       </c>
-      <c r="F9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>-4</v>
-      </c>
-      <c r="C10">
-        <v>-6</v>
-      </c>
-      <c r="D10">
-        <v>-2</v>
-      </c>
-      <c r="E10">
-        <v>-7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11">
-        <v>-2</v>
-      </c>
       <c r="C11">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="D11">
         <v>-7</v>
       </c>
       <c r="E11">
-        <v>-10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>89</v>
+        <v>-2</v>
+      </c>
+      <c r="F11">
+        <v>-12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Fantasy 2026 2026.xlsx
+++ b/data/leagues/Fantasy 2026 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="108">
   <si>
     <t>Fumbledore</t>
   </si>
@@ -55,22 +55,25 @@
     <t>Amanda's Awesome Team</t>
   </si>
   <si>
-    <t>4-1-0</t>
-  </si>
-  <si>
-    <t>3-2-0</t>
-  </si>
-  <si>
-    <t>2-3-0</t>
-  </si>
-  <si>
-    <t>1-4-0</t>
-  </si>
-  <si>
-    <t>5-0-0</t>
-  </si>
-  <si>
-    <t>0-5-0</t>
+    <t>4-2-0</t>
+  </si>
+  <si>
+    <t>3-3-0</t>
+  </si>
+  <si>
+    <t>5-1-0</t>
+  </si>
+  <si>
+    <t>2-4-0</t>
+  </si>
+  <si>
+    <t>1-5-0</t>
+  </si>
+  <si>
+    <t>6-0-0</t>
+  </si>
+  <si>
+    <t>0-6-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -142,6 +145,9 @@
     <t>Week_6</t>
   </si>
   <si>
+    <t>Week_7</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -163,36 +169,36 @@
     <t>Games_Remaining</t>
   </si>
   <si>
+    <t>Marianne Schulmeister</t>
+  </si>
+  <si>
+    <t>ashley Lavery</t>
+  </si>
+  <si>
+    <t>kaitlin hahn</t>
+  </si>
+  <si>
     <t>Michele Schul</t>
   </si>
   <si>
-    <t>ashley Lavery</t>
+    <t>chloe melvin</t>
+  </si>
+  <si>
+    <t>Amanda Pasquale</t>
+  </si>
+  <si>
+    <t>Madison Dietz</t>
   </si>
   <si>
     <t>Hilary Manion</t>
   </si>
   <si>
-    <t>kaitlin hahn</t>
-  </si>
-  <si>
-    <t>Marianne Schulmeister</t>
-  </si>
-  <si>
-    <t>chloe melvin</t>
-  </si>
-  <si>
-    <t>Amanda Pasquale</t>
-  </si>
-  <si>
-    <t>Madison Dietz</t>
+    <t>Meghan Bishop</t>
   </si>
   <si>
     <t>Shannon Finegan</t>
   </si>
   <si>
-    <t>Meghan Bishop</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -217,61 +223,55 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>9.8-4.1-0.1</t>
-  </si>
-  <si>
-    <t>9.1-4.8-0.1</t>
-  </si>
-  <si>
-    <t>8.5-5.4-0.1</t>
-  </si>
-  <si>
-    <t>7.4-6.5-0.1</t>
-  </si>
-  <si>
-    <t>7.3-6.6-0.1</t>
-  </si>
-  <si>
-    <t>6.7-7.2-0.1</t>
-  </si>
-  <si>
-    <t>5.9-8.0-0.1</t>
-  </si>
-  <si>
-    <t>5.1-8.8-0.1</t>
-  </si>
-  <si>
-    <t>4.9-9.0-0.1</t>
-  </si>
-  <si>
-    <t>4.7-9.2-0.1</t>
-  </si>
-  <si>
-    <t>10-4</t>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>8.8-5.1-0.1</t>
+  </si>
+  <si>
+    <t>8.4-5.5-0.1</t>
+  </si>
+  <si>
+    <t>7.8-6.1-0.1</t>
+  </si>
+  <si>
+    <t>8.0-5.9-0.1</t>
+  </si>
+  <si>
+    <t>7.5-6.4-0.1</t>
+  </si>
+  <si>
+    <t>6.9-7.0-0.1</t>
+  </si>
+  <si>
+    <t>6.2-7.7-0.1</t>
+  </si>
+  <si>
+    <t>5.7-8.2-0.1</t>
+  </si>
+  <si>
+    <t>4.4-9.5-0.1</t>
   </si>
   <si>
     <t>9-5</t>
   </si>
   <si>
+    <t>8-6</t>
+  </si>
+  <si>
     <t>7-7</t>
   </si>
   <si>
-    <t>8-6</t>
-  </si>
-  <si>
-    <t>5-9</t>
+    <t>6-8</t>
   </si>
   <si>
     <t>4-10</t>
@@ -286,36 +286,30 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑10</t>
+    <t>↑3</t>
+  </si>
+  <si>
+    <t>↑1</t>
   </si>
   <si>
     <t>↓1</t>
   </si>
   <si>
-    <t>↑3</t>
-  </si>
-  <si>
-    <t>↓5</t>
-  </si>
-  <si>
-    <t>↑7</t>
-  </si>
-  <si>
-    <t>↑5</t>
+    <t>0</t>
+  </si>
+  <si>
+    <t>↑6</t>
+  </si>
+  <si>
+    <t>↓2</t>
+  </si>
+  <si>
+    <t>↓6</t>
   </si>
   <si>
     <t>↓3</t>
   </si>
   <si>
-    <t>↑2</t>
-  </si>
-  <si>
-    <t>↓7</t>
-  </si>
-  <si>
-    <t>↓10</t>
-  </si>
-  <si>
     <t>Week 1</t>
   </si>
   <si>
@@ -329,6 +323,9 @@
   </si>
   <si>
     <t>Week 5</t>
+  </si>
+  <si>
+    <t>Week 6</t>
   </si>
   <si>
     <t>Week</t>
@@ -750,7 +747,7 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -765,13 +762,13 @@
         <v>10</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K2" t="s">
         <v>10</v>
@@ -785,31 +782,31 @@
         <v>11</v>
       </c>
       <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" t="s">
         <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -817,31 +814,31 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K4" t="s">
         <v>11</v>
@@ -855,7 +852,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -864,19 +861,19 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
         <v>13</v>
       </c>
-      <c r="H5" t="s">
-        <v>12</v>
-      </c>
       <c r="I5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" t="s">
         <v>13</v>
-      </c>
-      <c r="J5" t="s">
-        <v>12</v>
       </c>
       <c r="K5" t="s">
         <v>11</v>
@@ -887,34 +884,34 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
         <v>12</v>
       </c>
-      <c r="G6" t="s">
-        <v>10</v>
-      </c>
       <c r="H6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" t="s">
         <v>12</v>
-      </c>
-      <c r="I6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" t="s">
-        <v>11</v>
-      </c>
-      <c r="K6" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -922,34 +919,34 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
         <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -960,28 +957,28 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" t="s">
         <v>11</v>
       </c>
       <c r="I8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K8" t="s">
         <v>10</v>
@@ -998,28 +995,28 @@
         <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" t="s">
         <v>13</v>
       </c>
       <c r="J9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1030,31 +1027,31 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" t="s">
         <v>13</v>
-      </c>
-      <c r="I10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" t="s">
-        <v>12</v>
-      </c>
-      <c r="K10" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1065,28 +1062,28 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
         <v>12</v>
       </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
       <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" t="s">
         <v>12</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J11" t="s">
-        <v>10</v>
       </c>
       <c r="K11" t="s">
         <v>10</v>
@@ -1099,30 +1096,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1130,22 +1127,22 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="G2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
         <v>5</v>
@@ -1156,25 +1153,25 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>-8</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1182,25 +1179,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>-2</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>7</v>
       </c>
       <c r="H4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1208,25 +1205,25 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>-2</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5">
         <v>7</v>
       </c>
-      <c r="D5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>-5</v>
-      </c>
-      <c r="G5">
-        <v>6</v>
-      </c>
       <c r="H5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1234,25 +1231,25 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
         <v>0</v>
       </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
       <c r="E6">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1260,25 +1257,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>-14</v>
       </c>
       <c r="F7">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1286,22 +1283,22 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
         <v>2</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H8" t="s">
         <v>2</v>
@@ -1312,25 +1309,25 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9">
+        <v>-4</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
-      <c r="D9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9">
-        <v>-10</v>
-      </c>
-      <c r="F9">
-        <v>-7</v>
-      </c>
-      <c r="G9">
-        <v>3</v>
-      </c>
       <c r="H9" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1338,24 +1335,102 @@
         <v>8</v>
       </c>
       <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
         <v>3</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10">
+        <v>-1</v>
+      </c>
+      <c r="F10">
+        <v>-6</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>-2</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+      <c r="H11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12">
+        <v>-10</v>
+      </c>
+      <c r="F12">
+        <v>-7</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+      <c r="H12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s">
         <v>8</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D13" t="s">
         <v>4</v>
       </c>
-      <c r="E10">
+      <c r="E13">
         <v>1</v>
       </c>
-      <c r="F10">
+      <c r="F13">
         <v>0</v>
       </c>
-      <c r="G10">
+      <c r="G13">
         <v>1</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H13" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1371,13 +1446,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1385,13 +1460,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1402,10 +1477,10 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1413,13 +1488,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1430,7 +1505,7 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -1441,13 +1516,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1455,13 +1530,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1469,13 +1544,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1483,13 +1558,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1500,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -1514,10 +1589,10 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1532,16 +1607,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1549,16 +1624,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="D2">
-        <v>-0.8999999999999999</v>
+        <v>0.7000000000000002</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1566,16 +1641,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="D3">
-        <v>0.1000000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1583,16 +1658,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1600,16 +1675,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="D5">
-        <v>0.7999999999999998</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1617,16 +1692,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="D6">
-        <v>-0.2999999999999998</v>
+        <v>-0.8999999999999999</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1637,10 +1712,10 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="D7">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -1651,13 +1726,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8">
         <v>3</v>
       </c>
-      <c r="C8">
-        <v>2.3</v>
-      </c>
       <c r="D8">
-        <v>-0.7000000000000002</v>
+        <v>0</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
@@ -1668,16 +1743,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1685,16 +1760,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="D10">
-        <v>0.8999999999999999</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1702,16 +1777,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="D11">
-        <v>-0.3</v>
+        <v>1.2</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1726,40 +1801,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1767,37 +1842,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>54</v>
+        <v>36.8</v>
       </c>
       <c r="C2">
-        <v>23.1</v>
+        <v>20.5</v>
       </c>
       <c r="D2">
-        <v>12.8</v>
+        <v>16.1</v>
       </c>
       <c r="E2">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="G2">
+        <v>4.6</v>
+      </c>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1.4</v>
+      </c>
+      <c r="J2">
         <v>0.9</v>
       </c>
-      <c r="H2">
-        <v>1.1</v>
-      </c>
-      <c r="I2">
-        <v>0.3</v>
-      </c>
-      <c r="J2">
-        <v>0.1</v>
-      </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L2">
-        <v>98.5</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1805,37 +1880,37 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>22.8</v>
+        <v>21</v>
       </c>
       <c r="C3">
-        <v>28.8</v>
+        <v>20.6</v>
       </c>
       <c r="D3">
-        <v>21.7</v>
+        <v>18.2</v>
       </c>
       <c r="E3">
-        <v>12.6</v>
+        <v>14.4</v>
       </c>
       <c r="F3">
-        <v>6.7</v>
+        <v>10.4</v>
       </c>
       <c r="G3">
-        <v>3.8</v>
+        <v>7.5</v>
       </c>
       <c r="H3">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="I3">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J3">
+        <v>1.1</v>
+      </c>
+      <c r="K3">
         <v>0.4</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
       <c r="L3">
-        <v>96.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1843,189 +1918,189 @@
         <v>6</v>
       </c>
       <c r="B4">
+        <v>15.4</v>
+      </c>
+      <c r="C4">
+        <v>19.2</v>
+      </c>
+      <c r="D4">
+        <v>15.3</v>
+      </c>
+      <c r="E4">
         <v>16.3</v>
       </c>
-      <c r="C4">
-        <v>24.8</v>
-      </c>
-      <c r="D4">
-        <v>24</v>
-      </c>
-      <c r="E4">
-        <v>13.8</v>
-      </c>
       <c r="F4">
-        <v>9.9</v>
+        <v>13.4</v>
       </c>
       <c r="G4">
-        <v>5.8</v>
+        <v>8.5</v>
       </c>
       <c r="H4">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="I4">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="K4">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="L4">
-        <v>94.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5">
-        <v>2.3</v>
+        <v>11.8</v>
       </c>
       <c r="C5">
-        <v>8.5</v>
+        <v>15.7</v>
       </c>
       <c r="D5">
+        <v>15.3</v>
+      </c>
+      <c r="E5">
+        <v>15.5</v>
+      </c>
+      <c r="F5">
+        <v>15.6</v>
+      </c>
+      <c r="G5">
         <v>12.3</v>
       </c>
-      <c r="E5">
-        <v>20.3</v>
-      </c>
-      <c r="F5">
-        <v>17.6</v>
-      </c>
-      <c r="G5">
-        <v>15.2</v>
-      </c>
       <c r="H5">
-        <v>10.4</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
-        <v>7.9</v>
+        <v>5.1</v>
       </c>
       <c r="J5">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="K5">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="L5">
-        <v>76.2</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>2.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C6">
-        <v>5.6</v>
+        <v>12.3</v>
       </c>
       <c r="D6">
-        <v>13.4</v>
+        <v>16.2</v>
       </c>
       <c r="E6">
-        <v>17.7</v>
+        <v>14.8</v>
       </c>
       <c r="F6">
-        <v>18.2</v>
+        <v>13.6</v>
       </c>
       <c r="G6">
-        <v>17</v>
+        <v>11.8</v>
       </c>
       <c r="H6">
-        <v>10.8</v>
+        <v>11.5</v>
       </c>
       <c r="I6">
-        <v>7.6</v>
+        <v>4.3</v>
       </c>
       <c r="J6">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="L6">
-        <v>74.5</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>3.6</v>
+      </c>
+      <c r="C7">
+        <v>6.1</v>
+      </c>
+      <c r="D7">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="E7">
+        <v>12.2</v>
+      </c>
+      <c r="F7">
+        <v>15.2</v>
+      </c>
+      <c r="G7">
+        <v>17.4</v>
+      </c>
+      <c r="H7">
+        <v>12</v>
+      </c>
+      <c r="I7">
+        <v>13</v>
+      </c>
+      <c r="J7">
+        <v>7.2</v>
+      </c>
+      <c r="K7">
         <v>4</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>6.6</v>
-      </c>
-      <c r="D7">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="E7">
-        <v>15.3</v>
-      </c>
-      <c r="F7">
-        <v>18.4</v>
-      </c>
-      <c r="G7">
-        <v>17</v>
-      </c>
-      <c r="H7">
-        <v>14.4</v>
-      </c>
-      <c r="I7">
-        <v>10.1</v>
-      </c>
-      <c r="J7">
-        <v>5.7</v>
-      </c>
-      <c r="K7">
-        <v>2.8</v>
-      </c>
       <c r="L7">
-        <v>67</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B8">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="D8">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="E8">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="F8">
-        <v>11.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G8">
-        <v>13.8</v>
+        <v>12.2</v>
       </c>
       <c r="H8">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="I8">
-        <v>18.5</v>
+        <v>18.1</v>
       </c>
       <c r="J8">
-        <v>15</v>
+        <v>15.4</v>
       </c>
       <c r="K8">
-        <v>9</v>
+        <v>11.4</v>
       </c>
       <c r="L8">
-        <v>39</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2033,113 +2108,113 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="D9">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="E9">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="F9">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="G9">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="H9">
-        <v>15.7</v>
+        <v>18.4</v>
       </c>
       <c r="I9">
-        <v>20.6</v>
+        <v>19</v>
       </c>
       <c r="J9">
-        <v>19.6</v>
+        <v>21.7</v>
       </c>
       <c r="K9">
-        <v>19.7</v>
+        <v>10.8</v>
       </c>
       <c r="L9">
-        <v>24.4</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C10">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="D10">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="E10">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="F10">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="H10">
         <v>14</v>
       </c>
       <c r="I10">
-        <v>18.4</v>
+        <v>20.6</v>
       </c>
       <c r="J10">
-        <v>24.9</v>
+        <v>23.9</v>
       </c>
       <c r="K10">
-        <v>23.7</v>
+        <v>22.2</v>
       </c>
       <c r="L10">
-        <v>19</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C11">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D11">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E11">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="F11">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="G11">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="H11">
-        <v>9.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I11">
-        <v>14.6</v>
+        <v>12.2</v>
       </c>
       <c r="J11">
-        <v>24.4</v>
+        <v>22.4</v>
       </c>
       <c r="K11">
-        <v>40.9</v>
+        <v>48</v>
       </c>
       <c r="L11">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>
@@ -2149,30 +2224,33 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>39</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2183,223 +2261,253 @@
         <v>100</v>
       </c>
       <c r="D2">
-        <v>99.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E2">
-        <v>99.7</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F2">
-        <v>99.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="G2">
-        <v>98.90000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>95.5</v>
+      </c>
+      <c r="H2">
+        <v>94.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C3">
         <v>100</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="E3">
         <v>100</v>
       </c>
       <c r="F3">
-        <v>95.89999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="G3">
-        <v>97.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>89.2</v>
+      </c>
+      <c r="H3">
+        <v>92.30000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4">
-        <v>87.40000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="C4">
-        <v>33.4</v>
+        <v>32.2</v>
       </c>
       <c r="D4">
-        <v>24.8</v>
+        <v>26.4</v>
       </c>
       <c r="E4">
-        <v>73.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F4">
-        <v>92.90000000000001</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="G4">
-        <v>95.09999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="H4">
+        <v>86.09999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>45.2</v>
+      </c>
+      <c r="C5">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="D5">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="E5">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="F5">
+        <v>74.2</v>
+      </c>
+      <c r="G5">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="H5">
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>95.89999999999999</v>
+      </c>
+      <c r="C6">
+        <v>51.6</v>
+      </c>
+      <c r="D6">
+        <v>85.7</v>
+      </c>
+      <c r="E6">
+        <v>60.5</v>
+      </c>
+      <c r="F6">
+        <v>63</v>
+      </c>
+      <c r="G6">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="H6">
+        <v>80.90000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>2.5</v>
+      </c>
+      <c r="C7">
+        <v>2.4</v>
+      </c>
+      <c r="D7">
+        <v>1.4</v>
+      </c>
+      <c r="E7">
+        <v>22.5</v>
+      </c>
+      <c r="F7">
+        <v>39.2</v>
+      </c>
+      <c r="G7">
+        <v>61.9</v>
+      </c>
+      <c r="H7">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>68.5</v>
-      </c>
-      <c r="C5">
-        <v>94.89999999999999</v>
-      </c>
-      <c r="D5">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="E5">
-        <v>43.3</v>
-      </c>
-      <c r="F5">
-        <v>74.5</v>
-      </c>
-      <c r="G5">
-        <v>77.10000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>41.4</v>
-      </c>
-      <c r="C6">
-        <v>96.39999999999999</v>
-      </c>
-      <c r="D6">
-        <v>97.7</v>
-      </c>
-      <c r="E6">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="F6">
-        <v>74.8</v>
-      </c>
-      <c r="G6">
-        <v>72.09999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>95.19999999999999</v>
-      </c>
-      <c r="C7">
-        <v>51.1</v>
-      </c>
-      <c r="D7">
-        <v>84.5</v>
-      </c>
-      <c r="E7">
-        <v>62.8</v>
-      </c>
-      <c r="F7">
-        <v>63.7</v>
-      </c>
-      <c r="G7">
-        <v>65.60000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="B8">
-        <v>2.6</v>
+        <v>66.8</v>
       </c>
       <c r="C8">
-        <v>2.4</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D8">
-        <v>1.6</v>
+        <v>90.8</v>
       </c>
       <c r="E8">
-        <v>20.3</v>
+        <v>43.5</v>
       </c>
       <c r="F8">
-        <v>41.3</v>
+        <v>73</v>
       </c>
       <c r="G8">
-        <v>41.7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>43.1</v>
+      </c>
+      <c r="H8">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B9">
-        <v>53.5</v>
+        <v>49.4</v>
       </c>
       <c r="C9">
-        <v>5.600000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="D9">
-        <v>47.4</v>
+        <v>46.1</v>
       </c>
       <c r="E9">
-        <v>57.09999999999999</v>
+        <v>58.09999999999999</v>
       </c>
       <c r="F9">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="G9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>35.09999999999999</v>
+      </c>
+      <c r="H9">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>53.3</v>
+      </c>
+      <c r="C10">
+        <v>89.5</v>
+      </c>
+      <c r="D10">
+        <v>33.6</v>
+      </c>
+      <c r="E10">
+        <v>9</v>
+      </c>
+      <c r="F10">
+        <v>10.5</v>
+      </c>
+      <c r="G10">
+        <v>21.1</v>
+      </c>
+      <c r="H10">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>0.1</v>
       </c>
-      <c r="C10">
-        <v>27</v>
-      </c>
-      <c r="D10">
-        <v>19.6</v>
-      </c>
-      <c r="E10">
-        <v>35.3</v>
-      </c>
-      <c r="F10">
-        <v>18</v>
-      </c>
-      <c r="G10">
-        <v>16.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11">
-        <v>51.3</v>
-      </c>
       <c r="C11">
-        <v>89.2</v>
+        <v>27.2</v>
       </c>
       <c r="D11">
-        <v>32.7</v>
+        <v>18.9</v>
       </c>
       <c r="E11">
-        <v>8.9</v>
+        <v>34.3</v>
       </c>
       <c r="F11">
-        <v>10.8</v>
+        <v>19.5</v>
       </c>
       <c r="G11">
-        <v>10.6</v>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H11">
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -2414,28 +2522,28 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2443,28 +2551,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D2">
-        <v>119.9</v>
+        <v>115.59</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2">
-        <v>122.59</v>
+        <v>122.72</v>
       </c>
       <c r="G2">
-        <v>0.489</v>
+        <v>0.5</v>
       </c>
       <c r="H2">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2475,25 +2583,25 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>108.89</v>
+        <v>110.21</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>123.81</v>
+        <v>122.72</v>
       </c>
       <c r="G3">
-        <v>0.511</v>
+        <v>0.5</v>
       </c>
       <c r="H3">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2501,28 +2609,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>118.08</v>
+        <v>128.67</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>122.79</v>
+        <v>119.79</v>
       </c>
       <c r="G4">
-        <v>0.511</v>
+        <v>0.458</v>
       </c>
       <c r="H4">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2530,28 +2638,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5">
-        <v>134.62</v>
+        <v>120.61</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5">
-        <v>120.95</v>
+        <v>119.79</v>
       </c>
       <c r="G5">
-        <v>0.467</v>
+        <v>0.458</v>
       </c>
       <c r="H5">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2559,28 +2667,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6">
-        <v>120.88</v>
+        <v>124.62</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
       </c>
       <c r="F6">
-        <v>122.48</v>
+        <v>119.86</v>
       </c>
       <c r="G6">
-        <v>0.489</v>
+        <v>0.479</v>
       </c>
       <c r="H6">
-        <v>0.2</v>
+        <v>-0.5</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2588,28 +2696,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D7">
-        <v>124.16</v>
+        <v>124.06</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>122.12</v>
+        <v>119.86</v>
       </c>
       <c r="G7">
-        <v>0.511</v>
+        <v>0.479</v>
       </c>
       <c r="H7">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="I7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2617,28 +2725,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D8">
-        <v>128.18</v>
+        <v>115.51</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F8">
-        <v>121.67</v>
+        <v>121.52</v>
       </c>
       <c r="G8">
-        <v>0.467</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H8">
-        <v>-0.1</v>
+        <v>-2.1</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2646,28 +2754,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D9">
-        <v>116.83</v>
+        <v>119.61</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F9">
-        <v>122.93</v>
+        <v>119.89</v>
       </c>
       <c r="G9">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="H9">
-        <v>-0.6</v>
+        <v>-2.1</v>
       </c>
       <c r="I9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2675,28 +2783,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D10">
-        <v>119.99</v>
+        <v>128.8</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F10">
-        <v>122.58</v>
+        <v>119.89</v>
       </c>
       <c r="G10">
-        <v>0.533</v>
+        <v>0.5</v>
       </c>
       <c r="H10">
-        <v>-1.4</v>
+        <v>-2.1</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2704,28 +2812,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D11">
-        <v>131.67</v>
+        <v>119.87</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F11">
-        <v>121.28</v>
+        <v>121.52</v>
       </c>
       <c r="G11">
-        <v>0.489</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H11">
-        <v>-1.9</v>
+        <v>-2.1</v>
       </c>
       <c r="I11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2740,31 +2848,31 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2772,28 +2880,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C2">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D2">
-        <v>134.616</v>
+        <v>128.6733333333333</v>
       </c>
       <c r="E2">
-        <v>673.08</v>
+        <v>772.0400000000001</v>
       </c>
       <c r="F2">
-        <v>98.5</v>
+        <v>95.5</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2801,25 +2909,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C3">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
-        <v>128.18</v>
+        <v>124.0633333333333</v>
       </c>
       <c r="E3">
-        <v>640.9000000000001</v>
+        <v>744.3800000000001</v>
       </c>
       <c r="F3">
-        <v>96.39999999999999</v>
+        <v>92.10000000000001</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I3" t="s">
         <v>79</v>
@@ -2830,54 +2938,54 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4">
+        <v>0.5</v>
+      </c>
+      <c r="D4">
+        <v>128.8033333333333</v>
+      </c>
+      <c r="E4">
+        <v>772.8199999999999</v>
+      </c>
+      <c r="F4">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="G4">
         <v>0.6</v>
       </c>
-      <c r="D4">
-        <v>131.668</v>
-      </c>
-      <c r="E4">
-        <v>658.3399999999999</v>
-      </c>
-      <c r="F4">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="G4">
-        <v>0.2</v>
-      </c>
       <c r="H4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5">
-        <v>120.884</v>
+        <v>120.6133333333333</v>
       </c>
       <c r="E5">
-        <v>604.4200000000001</v>
+        <v>723.6799999999999</v>
       </c>
       <c r="F5">
-        <v>76.2</v>
+        <v>86.2</v>
       </c>
       <c r="G5">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="H5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I5" t="s">
         <v>80</v>
@@ -2885,86 +2993,86 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D6">
-        <v>119.904</v>
+        <v>124.62</v>
       </c>
       <c r="E6">
-        <v>599.52</v>
+        <v>747.72</v>
       </c>
       <c r="F6">
-        <v>74.5</v>
+        <v>78.5</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7">
+        <v>0.5</v>
+      </c>
+      <c r="D7">
+        <v>119.6133333333333</v>
+      </c>
+      <c r="E7">
+        <v>717.6799999999999</v>
+      </c>
+      <c r="F7">
+        <v>63.8</v>
+      </c>
+      <c r="G7">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7">
-        <v>0.4</v>
-      </c>
-      <c r="D7">
-        <v>124.156</v>
-      </c>
-      <c r="E7">
-        <v>620.78</v>
-      </c>
-      <c r="F7">
-        <v>67</v>
-      </c>
-      <c r="G7">
-        <v>2.8</v>
-      </c>
       <c r="H7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D8">
-        <v>118.076</v>
+        <v>115.59</v>
       </c>
       <c r="E8">
-        <v>590.38</v>
+        <v>693.5400000000001</v>
       </c>
       <c r="F8">
-        <v>39</v>
+        <v>36.8</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>11.4</v>
       </c>
       <c r="H8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I8" t="s">
         <v>82</v>
@@ -2975,25 +3083,25 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C9">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D9">
-        <v>119.988</v>
+        <v>119.8733333333333</v>
       </c>
       <c r="E9">
-        <v>599.9399999999999</v>
+        <v>719.2399999999999</v>
       </c>
       <c r="F9">
-        <v>24.4</v>
+        <v>30.1</v>
       </c>
       <c r="G9">
-        <v>19.7</v>
+        <v>10.8</v>
       </c>
       <c r="H9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I9" t="s">
         <v>82</v>
@@ -3001,28 +3109,28 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>67</v>
       </c>
       <c r="C10">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D10">
-        <v>116.828</v>
+        <v>110.21</v>
       </c>
       <c r="E10">
-        <v>584.14</v>
+        <v>661.2599999999999</v>
       </c>
       <c r="F10">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="G10">
-        <v>23.7</v>
+        <v>22.2</v>
       </c>
       <c r="H10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I10" t="s">
         <v>82</v>
@@ -3030,28 +3138,28 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C11">
-        <v>0.4</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D11">
-        <v>108.892</v>
+        <v>115.51</v>
       </c>
       <c r="E11">
-        <v>544.4599999999999</v>
+        <v>693.0599999999999</v>
       </c>
       <c r="F11">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
       <c r="G11">
-        <v>40.9</v>
+        <v>48</v>
       </c>
       <c r="H11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I11" t="s">
         <v>83</v>
@@ -3069,7 +3177,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>84</v>
@@ -3078,7 +3186,7 @@
         <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>86</v>
@@ -3092,10 +3200,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
@@ -3112,10 +3220,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -3132,13 +3240,13 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
         <v>89</v>
@@ -3149,19 +3257,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
         <v>52</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3169,19 +3277,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3189,10 +3297,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D7">
         <v>-2</v>
@@ -3201,7 +3309,7 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3212,16 +3320,16 @@
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3229,7 +3337,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
         <v>48</v>
@@ -3238,10 +3346,10 @@
         <v>-8</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3249,19 +3357,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D10">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3269,19 +3377,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D11">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -3291,30 +3399,33 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -3333,11 +3444,14 @@
       <c r="F2">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -3356,11 +3470,14 @@
       <c r="F3">
         <v>13</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -3379,80 +3496,92 @@
       <c r="F4">
         <v>5</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4">
+        <v>4</v>
+      </c>
+      <c r="H4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="H5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>-2</v>
+      </c>
+      <c r="C7">
+        <v>-2</v>
+      </c>
+      <c r="D7">
+        <v>-7</v>
+      </c>
+      <c r="E7">
+        <v>-10</v>
+      </c>
+      <c r="F7">
+        <v>-8</v>
+      </c>
+      <c r="G7">
+        <v>-2</v>
+      </c>
+      <c r="H7" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7">
-        <v>-4</v>
-      </c>
-      <c r="C7">
-        <v>-6</v>
-      </c>
-      <c r="D7">
-        <v>-2</v>
-      </c>
-      <c r="E7">
-        <v>-7</v>
-      </c>
-      <c r="F7">
-        <v>-2</v>
-      </c>
-      <c r="G7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -3471,77 +3600,89 @@
       <c r="F8">
         <v>-4</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8">
+        <v>-6</v>
+      </c>
+      <c r="H8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>-4</v>
+      </c>
+      <c r="C9">
+        <v>-6</v>
+      </c>
+      <c r="D9">
+        <v>-2</v>
+      </c>
+      <c r="E9">
+        <v>-7</v>
+      </c>
+      <c r="F9">
+        <v>-2</v>
+      </c>
+      <c r="G9">
+        <v>-8</v>
+      </c>
+      <c r="H9" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9">
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>-6</v>
+      </c>
+      <c r="C10">
+        <v>-5</v>
+      </c>
+      <c r="D10">
+        <v>-7</v>
+      </c>
+      <c r="E10">
         <v>-2</v>
       </c>
-      <c r="C9">
-        <v>-2</v>
-      </c>
-      <c r="D9">
-        <v>-7</v>
-      </c>
-      <c r="E9">
-        <v>-10</v>
-      </c>
-      <c r="F9">
-        <v>-8</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="F10">
+        <v>-12</v>
+      </c>
+      <c r="G10">
+        <v>-12</v>
+      </c>
+      <c r="H10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>-4</v>
+      </c>
+      <c r="F11">
+        <v>-11</v>
+      </c>
+      <c r="G11">
+        <v>-14</v>
+      </c>
+      <c r="H11" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>-4</v>
-      </c>
-      <c r="F10">
-        <v>-11</v>
-      </c>
-      <c r="G10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11">
-        <v>-6</v>
-      </c>
-      <c r="C11">
-        <v>-5</v>
-      </c>
-      <c r="D11">
-        <v>-7</v>
-      </c>
-      <c r="E11">
-        <v>-2</v>
-      </c>
-      <c r="F11">
-        <v>-12</v>
-      </c>
-      <c r="G11" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Fantasy 2026 2026.xlsx
+++ b/data/leagues/Fantasy 2026 2026.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="111">
   <si>
     <t>Fumbledore</t>
   </si>
@@ -55,25 +55,25 @@
     <t>Amanda's Awesome Team</t>
   </si>
   <si>
-    <t>4-2-0</t>
-  </si>
-  <si>
-    <t>3-3-0</t>
-  </si>
-  <si>
-    <t>5-1-0</t>
-  </si>
-  <si>
-    <t>2-4-0</t>
-  </si>
-  <si>
-    <t>1-5-0</t>
-  </si>
-  <si>
-    <t>6-0-0</t>
-  </si>
-  <si>
-    <t>0-6-0</t>
+    <t>5-2-0</t>
+  </si>
+  <si>
+    <t>4-3-0</t>
+  </si>
+  <si>
+    <t>6-1-0</t>
+  </si>
+  <si>
+    <t>3-4-0</t>
+  </si>
+  <si>
+    <t>2-5-0</t>
+  </si>
+  <si>
+    <t>7-0-0</t>
+  </si>
+  <si>
+    <t>1-6-0</t>
   </si>
   <si>
     <t>Teams</t>
@@ -148,6 +148,9 @@
     <t>Week_7</t>
   </si>
   <si>
+    <t>Week_8</t>
+  </si>
+  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -172,33 +175,33 @@
     <t>Marianne Schulmeister</t>
   </si>
   <si>
+    <t>kaitlin hahn</t>
+  </si>
+  <si>
     <t>ashley Lavery</t>
   </si>
   <si>
-    <t>kaitlin hahn</t>
+    <t>chloe melvin</t>
   </si>
   <si>
     <t>Michele Schul</t>
   </si>
   <si>
-    <t>chloe melvin</t>
+    <t>Shannon Finegan</t>
+  </si>
+  <si>
+    <t>Madison Dietz</t>
+  </si>
+  <si>
+    <t>Meghan Bishop</t>
+  </si>
+  <si>
+    <t>Hilary Manion</t>
   </si>
   <si>
     <t>Amanda Pasquale</t>
   </si>
   <si>
-    <t>Madison Dietz</t>
-  </si>
-  <si>
-    <t>Hilary Manion</t>
-  </si>
-  <si>
-    <t>Meghan Bishop</t>
-  </si>
-  <si>
-    <t>Shannon Finegan</t>
-  </si>
-  <si>
     <t>Current_Record</t>
   </si>
   <si>
@@ -223,58 +226,61 @@
     <t>Most_Likely_Record</t>
   </si>
   <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>8.8-5.1-0.1</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>9.4-4.5-0.1</t>
+  </si>
+  <si>
+    <t>9.0-4.9-0.1</t>
   </si>
   <si>
     <t>8.4-5.5-0.1</t>
   </si>
   <si>
-    <t>7.8-6.1-0.1</t>
-  </si>
-  <si>
-    <t>8.0-5.9-0.1</t>
-  </si>
-  <si>
-    <t>7.5-6.4-0.1</t>
-  </si>
-  <si>
-    <t>6.9-7.0-0.1</t>
+    <t>7.3-6.6-0.1</t>
+  </si>
+  <si>
+    <t>6.7-7.2-0.1</t>
   </si>
   <si>
     <t>6.2-7.7-0.1</t>
   </si>
   <si>
-    <t>5.7-8.2-0.1</t>
-  </si>
-  <si>
-    <t>4.4-9.5-0.1</t>
+    <t>6.4-7.5-0.1</t>
+  </si>
+  <si>
+    <t>5.9-8.0-0.1</t>
+  </si>
+  <si>
+    <t>5.2-8.7-0.1</t>
+  </si>
+  <si>
+    <t>4.9-9.0-0.1</t>
+  </si>
+  <si>
+    <t>10-4</t>
   </si>
   <si>
     <t>9-5</t>
   </si>
   <si>
-    <t>8-6</t>
-  </si>
-  <si>
     <t>7-7</t>
   </si>
   <si>
     <t>6-8</t>
   </si>
   <si>
-    <t>4-10</t>
+    <t>5-9</t>
   </si>
   <si>
     <t>Owners</t>
@@ -286,28 +292,28 @@
     <t>Change From Last Week</t>
   </si>
   <si>
-    <t>↑3</t>
+    <t>↓1</t>
+  </si>
+  <si>
+    <t>↓4</t>
   </si>
   <si>
     <t>↑1</t>
   </si>
   <si>
-    <t>↓1</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>↑6</t>
+    <t>↑5</t>
+  </si>
+  <si>
+    <t>↓3</t>
   </si>
   <si>
     <t>↓2</t>
   </si>
   <si>
-    <t>↓6</t>
-  </si>
-  <si>
-    <t>↓3</t>
+    <t>↑2</t>
+  </si>
+  <si>
+    <t>↑4</t>
   </si>
   <si>
     <t>Week 1</t>
@@ -326,6 +332,9 @@
   </si>
   <si>
     <t>Week 6</t>
+  </si>
+  <si>
+    <t>Week 7</t>
   </si>
   <si>
     <t>Week</t>
@@ -756,7 +765,7 @@
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
         <v>10</v>
@@ -788,10 +797,10 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -806,7 +815,7 @@
         <v>11</v>
       </c>
       <c r="K3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -849,7 +858,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
@@ -858,25 +867,25 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
         <v>13</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J5" t="s">
         <v>13</v>
       </c>
       <c r="K5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -884,34 +893,34 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
       <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
         <v>10</v>
       </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" t="s">
-        <v>12</v>
-      </c>
       <c r="H6" t="s">
         <v>13</v>
       </c>
       <c r="I6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J6" t="s">
         <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -919,34 +928,34 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7" t="s">
         <v>10</v>
       </c>
       <c r="K7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -963,10 +972,10 @@
         <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -989,34 +998,34 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
         <v>10</v>
       </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
       </c>
       <c r="I9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1033,13 +1042,13 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H10" t="s">
         <v>14</v>
@@ -1051,7 +1060,7 @@
         <v>11</v>
       </c>
       <c r="K10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1059,34 +1068,34 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" t="s">
         <v>10</v>
       </c>
-      <c r="H11" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" t="s">
-        <v>12</v>
-      </c>
       <c r="K11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1096,30 +1105,30 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1127,25 +1136,25 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>-2</v>
+        <v>-17</v>
       </c>
       <c r="G2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1153,22 +1162,22 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="G3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
         <v>5</v>
@@ -1179,25 +1188,25 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>-8</v>
       </c>
       <c r="G4">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1205,25 +1214,25 @@
         <v>3</v>
       </c>
       <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5">
         <v>5</v>
       </c>
-      <c r="C5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>-2</v>
-      </c>
       <c r="F5">
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1231,25 +1240,25 @@
         <v>4</v>
       </c>
       <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" t="s">
-        <v>2</v>
-      </c>
       <c r="D6" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>-12</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>-6</v>
+        <v>14</v>
       </c>
       <c r="G6">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
         <v>6</v>
-      </c>
-      <c r="H6" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1257,25 +1266,25 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>-2</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
         <v>3</v>
-      </c>
-      <c r="E7">
-        <v>-14</v>
-      </c>
-      <c r="F7">
-        <v>-8</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-      <c r="H7" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1309,25 +1318,25 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" t="s">
         <v>0</v>
       </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
       <c r="E9">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H9" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1335,25 +1344,25 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10" t="s">
         <v>3</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>-14</v>
       </c>
       <c r="F10">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1361,25 +1370,25 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="F11">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="G11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1387,25 +1396,25 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12">
+        <v>-4</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
         <v>5</v>
       </c>
-      <c r="D12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12">
-        <v>-10</v>
-      </c>
-      <c r="F12">
-        <v>-7</v>
-      </c>
-      <c r="G12">
-        <v>3</v>
-      </c>
       <c r="H12" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1413,25 +1422,51 @@
         <v>11</v>
       </c>
       <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>-2</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" t="s">
         <v>3</v>
       </c>
-      <c r="C13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13" t="s">
-        <v>4</v>
+      <c r="E14">
+        <v>-10</v>
+      </c>
+      <c r="F14">
+        <v>-7</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+      <c r="H14" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1460,13 +1495,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1477,7 +1512,7 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -1488,13 +1523,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1505,10 +1540,10 @@
         <v>3</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1516,13 +1551,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1533,10 +1568,10 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1544,13 +1579,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1558,13 +1593,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1572,13 +1607,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="D10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1589,7 +1624,7 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -1624,16 +1659,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="D2">
-        <v>0.7000000000000002</v>
+        <v>-0.5</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1641,16 +1676,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="D3">
-        <v>-0.5</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1658,16 +1693,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D4">
-        <v>0.5</v>
+        <v>-1</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1675,16 +1710,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="D5">
-        <v>-0.7000000000000002</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1692,16 +1727,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="D6">
-        <v>-0.8999999999999999</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1709,13 +1744,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="D7">
-        <v>1.1</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -1726,16 +1761,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1743,13 +1778,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="D9">
-        <v>-0.7000000000000002</v>
+        <v>-1.1</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -1760,16 +1795,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="D10">
-        <v>-0.7000000000000002</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1777,16 +1812,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="D11">
-        <v>1.2</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="E11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1842,75 +1877,75 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>36.8</v>
+        <v>49.5</v>
       </c>
       <c r="C2">
-        <v>20.5</v>
+        <v>27.2</v>
       </c>
       <c r="D2">
-        <v>16.1</v>
+        <v>12.9</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>5.9</v>
       </c>
       <c r="F2">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="G2">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="I2">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="J2">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="K2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>95.5</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>21</v>
+        <v>24.1</v>
       </c>
       <c r="C3">
-        <v>20.6</v>
+        <v>31.4</v>
       </c>
       <c r="D3">
-        <v>18.2</v>
+        <v>23.4</v>
       </c>
       <c r="E3">
-        <v>14.4</v>
+        <v>11.5</v>
       </c>
       <c r="F3">
-        <v>10.4</v>
+        <v>5.1</v>
       </c>
       <c r="G3">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="H3">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="I3">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J3">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="K3">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="L3">
-        <v>92.09999999999999</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1918,75 +1953,75 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>15.4</v>
+        <v>21.8</v>
       </c>
       <c r="C4">
-        <v>19.2</v>
+        <v>24.3</v>
       </c>
       <c r="D4">
-        <v>15.3</v>
+        <v>26.7</v>
       </c>
       <c r="E4">
-        <v>16.3</v>
+        <v>13.2</v>
       </c>
       <c r="F4">
-        <v>13.4</v>
+        <v>5.7</v>
       </c>
       <c r="G4">
-        <v>8.5</v>
+        <v>3.2</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>3.2</v>
       </c>
       <c r="I4">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J4">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="K4">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="L4">
-        <v>88.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>11.8</v>
+        <v>2.1</v>
       </c>
       <c r="C5">
-        <v>15.7</v>
+        <v>6.5</v>
       </c>
       <c r="D5">
-        <v>15.3</v>
+        <v>12.8</v>
       </c>
       <c r="E5">
-        <v>15.5</v>
+        <v>20.7</v>
       </c>
       <c r="F5">
-        <v>15.6</v>
+        <v>20.1</v>
       </c>
       <c r="G5">
-        <v>12.3</v>
+        <v>12.8</v>
       </c>
       <c r="H5">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="I5">
-        <v>5.1</v>
+        <v>6.9</v>
       </c>
       <c r="J5">
-        <v>1.7</v>
+        <v>4.9</v>
       </c>
       <c r="K5">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="L5">
-        <v>86.2</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1994,37 +2029,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>9.800000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="C6">
-        <v>12.3</v>
+        <v>5.4</v>
       </c>
       <c r="D6">
-        <v>16.2</v>
+        <v>9.6</v>
       </c>
       <c r="E6">
-        <v>14.8</v>
+        <v>15.8</v>
       </c>
       <c r="F6">
-        <v>13.6</v>
+        <v>16.9</v>
       </c>
       <c r="G6">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="H6">
-        <v>11.5</v>
+        <v>12.7</v>
       </c>
       <c r="I6">
-        <v>4.3</v>
+        <v>10.1</v>
       </c>
       <c r="J6">
-        <v>4.1</v>
+        <v>6.9</v>
       </c>
       <c r="K6">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="L6">
-        <v>78.5</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2032,189 +2067,189 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="C7">
-        <v>6.1</v>
+        <v>1.3</v>
       </c>
       <c r="D7">
-        <v>9.300000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="E7">
-        <v>12.2</v>
+        <v>12.7</v>
       </c>
       <c r="F7">
-        <v>15.2</v>
+        <v>14.4</v>
       </c>
       <c r="G7">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="H7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I7">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="J7">
-        <v>7.2</v>
+        <v>11.2</v>
       </c>
       <c r="K7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>63.8</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C8">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D8">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="F8">
-        <v>9.699999999999999</v>
+        <v>13.2</v>
       </c>
       <c r="G8">
-        <v>12.2</v>
+        <v>14.5</v>
       </c>
       <c r="H8">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="I8">
-        <v>18.1</v>
+        <v>15</v>
       </c>
       <c r="J8">
-        <v>15.4</v>
+        <v>16.6</v>
       </c>
       <c r="K8">
-        <v>11.4</v>
+        <v>8.9</v>
       </c>
       <c r="L8">
-        <v>36.8</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B9">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C9">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="D9">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="E9">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="F9">
-        <v>7.8</v>
+        <v>9.9</v>
       </c>
       <c r="G9">
-        <v>11.5</v>
+        <v>14.2</v>
       </c>
       <c r="H9">
-        <v>18.4</v>
+        <v>14.2</v>
       </c>
       <c r="I9">
-        <v>19</v>
+        <v>17.1</v>
       </c>
       <c r="J9">
-        <v>21.7</v>
+        <v>17.4</v>
       </c>
       <c r="K9">
-        <v>10.8</v>
+        <v>15.3</v>
       </c>
       <c r="L9">
-        <v>30.1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B10">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C10">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="D10">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="E10">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>6.9</v>
       </c>
       <c r="G10">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="H10">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="I10">
-        <v>20.6</v>
+        <v>18.3</v>
       </c>
       <c r="J10">
-        <v>23.9</v>
+        <v>20.9</v>
       </c>
       <c r="K10">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="L10">
-        <v>19.3</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B11">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D11">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E11">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="H11">
-        <v>7.8</v>
+        <v>12.4</v>
       </c>
       <c r="I11">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="J11">
-        <v>22.4</v>
+        <v>21</v>
       </c>
       <c r="K11">
-        <v>48</v>
+        <v>35.2</v>
       </c>
       <c r="L11">
-        <v>9.6</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2224,10 +2259,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
         <v>34</v>
       </c>
@@ -2249,8 +2284,11 @@
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2261,253 +2299,283 @@
         <v>100</v>
       </c>
       <c r="D2">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E2">
+        <v>99.8</v>
+      </c>
+      <c r="F2">
         <v>99.59999999999999</v>
       </c>
-      <c r="E2">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="F2">
-        <v>99.40000000000001</v>
-      </c>
       <c r="G2">
-        <v>95.5</v>
+        <v>95.89999999999999</v>
       </c>
       <c r="H2">
-        <v>94.3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>99.2</v>
+      </c>
+      <c r="I2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B3">
-        <v>99.90000000000001</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D3">
-        <v>99.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="F3">
-        <v>96.8</v>
+        <v>73.2</v>
       </c>
       <c r="G3">
-        <v>89.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="H3">
-        <v>92.30000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>97.2</v>
+      </c>
+      <c r="I3">
+        <v>98.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B4">
-        <v>86.90000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="C4">
-        <v>32.2</v>
+        <v>31.1</v>
       </c>
       <c r="D4">
-        <v>26.4</v>
+        <v>27.2</v>
       </c>
       <c r="E4">
-        <v>73.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="F4">
-        <v>95.19999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="G4">
-        <v>86.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="H4">
-        <v>86.09999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>96.89999999999999</v>
+      </c>
+      <c r="I4">
+        <v>96.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>45.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
         <v>96.59999999999999</v>
       </c>
-      <c r="D5">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="E5">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="F5">
-        <v>74.2</v>
-      </c>
       <c r="G5">
-        <v>79.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H5">
-        <v>83.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="I5">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>95.89999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="C6">
-        <v>51.6</v>
+        <v>50.4</v>
       </c>
       <c r="D6">
-        <v>85.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E6">
-        <v>60.5</v>
+        <v>61.3</v>
       </c>
       <c r="F6">
-        <v>63</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G6">
-        <v>78.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="H6">
-        <v>80.90000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>63.6</v>
+      </c>
+      <c r="I6">
+        <v>64.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="C7">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="D7">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E7">
-        <v>22.5</v>
+        <v>19.3</v>
       </c>
       <c r="F7">
-        <v>39.2</v>
+        <v>39.4</v>
       </c>
       <c r="G7">
-        <v>61.9</v>
+        <v>59</v>
       </c>
       <c r="H7">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>52.5</v>
+      </c>
+      <c r="I7">
+        <v>48.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B8">
-        <v>66.8</v>
+        <v>63.8</v>
       </c>
       <c r="C8">
-        <v>95.59999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D8">
-        <v>90.8</v>
+        <v>89.60000000000001</v>
       </c>
       <c r="E8">
-        <v>43.5</v>
+        <v>42.8</v>
       </c>
       <c r="F8">
-        <v>73</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G8">
-        <v>43.1</v>
+        <v>41.3</v>
       </c>
       <c r="H8">
-        <v>43.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>32.3</v>
+      </c>
+      <c r="I8">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>54.2</v>
+      </c>
+      <c r="C9">
+        <v>90.3</v>
+      </c>
+      <c r="D9">
+        <v>33.5</v>
+      </c>
+      <c r="E9">
+        <v>10.2</v>
+      </c>
+      <c r="F9">
+        <v>10.5</v>
+      </c>
+      <c r="G9">
+        <v>20.3</v>
+      </c>
+      <c r="H9">
+        <v>39</v>
+      </c>
+      <c r="I9">
+        <v>37.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>0.1</v>
+      </c>
+      <c r="C10">
+        <v>28.5</v>
+      </c>
+      <c r="D10">
+        <v>18.7</v>
+      </c>
+      <c r="E10">
+        <v>34.7</v>
+      </c>
+      <c r="F10">
+        <v>20</v>
+      </c>
+      <c r="G10">
+        <v>7.399999999999999</v>
+      </c>
+      <c r="H10">
+        <v>24</v>
+      </c>
+      <c r="I10">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B9">
-        <v>49.4</v>
-      </c>
-      <c r="C9">
-        <v>4.9</v>
-      </c>
-      <c r="D9">
-        <v>46.1</v>
-      </c>
-      <c r="E9">
-        <v>58.09999999999999</v>
-      </c>
-      <c r="F9">
-        <v>29.2</v>
-      </c>
-      <c r="G9">
-        <v>35.09999999999999</v>
-      </c>
-      <c r="H9">
-        <v>32.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10">
-        <v>53.3</v>
-      </c>
-      <c r="C10">
-        <v>89.5</v>
-      </c>
-      <c r="D10">
-        <v>33.6</v>
-      </c>
-      <c r="E10">
-        <v>9</v>
-      </c>
-      <c r="F10">
-        <v>10.5</v>
-      </c>
-      <c r="G10">
-        <v>21.1</v>
-      </c>
-      <c r="H10">
-        <v>16.7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="B11">
-        <v>0.1</v>
+        <v>49.8</v>
       </c>
       <c r="C11">
-        <v>27.2</v>
+        <v>5.7</v>
       </c>
       <c r="D11">
-        <v>18.9</v>
+        <v>45.8</v>
       </c>
       <c r="E11">
-        <v>34.3</v>
+        <v>58.59999999999999</v>
       </c>
       <c r="F11">
-        <v>19.5</v>
+        <v>25.2</v>
       </c>
       <c r="G11">
-        <v>9.199999999999999</v>
+        <v>37.2</v>
       </c>
       <c r="H11">
-        <v>6.9</v>
+        <v>20.4</v>
+      </c>
+      <c r="I11">
+        <v>18.7</v>
       </c>
     </row>
   </sheetData>
@@ -2525,25 +2593,25 @@
         <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2554,25 +2622,25 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2">
-        <v>115.59</v>
+        <v>114.32</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2">
-        <v>122.72</v>
+        <v>120.68</v>
       </c>
       <c r="G2">
-        <v>0.5</v>
+        <v>0.469</v>
       </c>
       <c r="H2">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2580,28 +2648,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3">
-        <v>110.21</v>
+        <v>131.05</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>122.72</v>
+        <v>118.76</v>
       </c>
       <c r="G3">
-        <v>0.5</v>
+        <v>0.449</v>
       </c>
       <c r="H3">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2609,28 +2677,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4">
-        <v>128.67</v>
+        <v>110.81</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>119.79</v>
+        <v>122.79</v>
       </c>
       <c r="G4">
-        <v>0.458</v>
+        <v>0.531</v>
       </c>
       <c r="H4">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2638,28 +2706,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5">
-        <v>120.61</v>
+        <v>120.94</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F5">
-        <v>119.79</v>
+        <v>119.76</v>
       </c>
       <c r="G5">
-        <v>0.458</v>
+        <v>0.469</v>
       </c>
       <c r="H5">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2667,28 +2735,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6">
-        <v>124.62</v>
+        <v>124.24</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>119.86</v>
+        <v>117.82</v>
       </c>
       <c r="G6">
-        <v>0.479</v>
+        <v>0.449</v>
       </c>
       <c r="H6">
-        <v>-0.5</v>
+        <v>0.7</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2696,28 +2764,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7">
-        <v>124.06</v>
+        <v>116.31</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F7">
-        <v>119.86</v>
+        <v>122.28</v>
       </c>
       <c r="G7">
-        <v>0.479</v>
+        <v>0.551</v>
       </c>
       <c r="H7">
-        <v>-0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2728,25 +2796,25 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D8">
-        <v>115.51</v>
+        <v>117.92</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
       </c>
       <c r="F8">
-        <v>121.52</v>
+        <v>121.35</v>
       </c>
       <c r="G8">
-        <v>0.5620000000000001</v>
+        <v>0.571</v>
       </c>
       <c r="H8">
-        <v>-2.1</v>
+        <v>-1.4</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2754,28 +2822,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9">
-        <v>119.61</v>
+        <v>130.64</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9">
-        <v>119.89</v>
+        <v>119.37</v>
       </c>
       <c r="G9">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="H9">
-        <v>-2.1</v>
+        <v>-1.7</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2783,28 +2851,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10">
-        <v>128.8</v>
+        <v>117.29</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>119.89</v>
+        <v>119.3</v>
       </c>
       <c r="G10">
-        <v>0.5</v>
+        <v>0.531</v>
       </c>
       <c r="H10">
-        <v>-2.1</v>
+        <v>-2.7</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2812,28 +2880,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11">
+        <v>117.44</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11">
+        <v>118.85</v>
+      </c>
+      <c r="G11">
+        <v>0.49</v>
+      </c>
+      <c r="H11">
+        <v>-3</v>
+      </c>
+      <c r="I11">
         <v>7</v>
-      </c>
-      <c r="C11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11">
-        <v>119.87</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11">
-        <v>121.52</v>
-      </c>
-      <c r="G11">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="H11">
-        <v>-2.1</v>
-      </c>
-      <c r="I11">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2851,28 +2919,28 @@
         <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2880,57 +2948,57 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D2">
-        <v>128.6733333333333</v>
+        <v>131.0485714285714</v>
       </c>
       <c r="E2">
-        <v>772.0400000000001</v>
+        <v>917.3400000000001</v>
       </c>
       <c r="F2">
-        <v>95.5</v>
+        <v>99.3</v>
       </c>
       <c r="G2">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D3">
-        <v>124.0633333333333</v>
+        <v>124.2428571428571</v>
       </c>
       <c r="E3">
-        <v>744.3800000000001</v>
+        <v>869.6999999999999</v>
       </c>
       <c r="F3">
-        <v>92.10000000000001</v>
+        <v>98</v>
       </c>
       <c r="G3">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2938,57 +3006,57 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D4">
-        <v>128.8033333333333</v>
+        <v>130.6428571428571</v>
       </c>
       <c r="E4">
-        <v>772.8199999999999</v>
+        <v>914.5</v>
       </c>
       <c r="F4">
-        <v>88.09999999999999</v>
+        <v>94.89999999999999</v>
       </c>
       <c r="G4">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D5">
-        <v>120.6133333333333</v>
+        <v>117.44</v>
       </c>
       <c r="E5">
-        <v>723.6799999999999</v>
+        <v>822.0800000000002</v>
       </c>
       <c r="F5">
-        <v>86.2</v>
+        <v>75</v>
       </c>
       <c r="G5">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="H5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2996,28 +3064,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D6">
-        <v>124.62</v>
+        <v>120.94</v>
       </c>
       <c r="E6">
-        <v>747.72</v>
+        <v>846.58</v>
       </c>
       <c r="F6">
-        <v>78.5</v>
+        <v>64.60000000000001</v>
       </c>
       <c r="G6">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="H6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I6" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3025,144 +3093,144 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C7">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D7">
-        <v>119.6133333333333</v>
+        <v>117.2885714285714</v>
       </c>
       <c r="E7">
-        <v>717.6799999999999</v>
+        <v>821.02</v>
       </c>
       <c r="F7">
-        <v>63.8</v>
+        <v>49.7</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D8">
-        <v>115.59</v>
+        <v>110.8057142857143</v>
       </c>
       <c r="E8">
-        <v>693.5400000000001</v>
+        <v>775.6399999999999</v>
       </c>
       <c r="F8">
-        <v>36.8</v>
+        <v>40.9</v>
       </c>
       <c r="G8">
-        <v>11.4</v>
+        <v>8.9</v>
       </c>
       <c r="H8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D9">
-        <v>119.8733333333333</v>
+        <v>114.3228571428572</v>
       </c>
       <c r="E9">
-        <v>719.2399999999999</v>
+        <v>800.2600000000001</v>
       </c>
       <c r="F9">
-        <v>30.1</v>
+        <v>36</v>
       </c>
       <c r="G9">
-        <v>10.8</v>
+        <v>15.3</v>
       </c>
       <c r="H9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D10">
-        <v>110.21</v>
+        <v>117.92</v>
       </c>
       <c r="E10">
-        <v>661.2599999999999</v>
+        <v>825.4399999999999</v>
       </c>
       <c r="F10">
-        <v>19.3</v>
+        <v>24.6</v>
       </c>
       <c r="G10">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C11">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D11">
-        <v>115.51</v>
+        <v>116.3085714285714</v>
       </c>
       <c r="E11">
-        <v>693.0599999999999</v>
+        <v>814.1599999999999</v>
       </c>
       <c r="F11">
-        <v>9.6</v>
+        <v>17</v>
       </c>
       <c r="G11">
-        <v>48</v>
+        <v>35.2</v>
       </c>
       <c r="H11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -3180,16 +3248,16 @@
         <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3203,13 +3271,13 @@
         <v>56</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3220,16 +3288,16 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3240,16 +3308,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3263,13 +3331,13 @@
         <v>52</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3277,19 +3345,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3297,10 +3365,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D7">
         <v>-2</v>
@@ -3309,7 +3377,7 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3317,19 +3385,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D8">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3340,16 +3408,16 @@
         <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3360,16 +3428,16 @@
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D10">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3380,16 +3448,16 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D11">
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -3399,33 +3467,36 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+        <v>103</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -3447,11 +3518,14 @@
       <c r="G2">
         <v>20</v>
       </c>
-      <c r="H2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="H2">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -3473,11 +3547,14 @@
       <c r="G3">
         <v>14</v>
       </c>
-      <c r="H3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="H3">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -3499,11 +3576,14 @@
       <c r="G4">
         <v>4</v>
       </c>
-      <c r="H4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="H4">
+        <v>5</v>
+      </c>
+      <c r="I4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -3525,89 +3605,101 @@
       <c r="G5">
         <v>4</v>
       </c>
-      <c r="H5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>-1</v>
+      </c>
+      <c r="F6">
+        <v>-4</v>
+      </c>
+      <c r="G6">
+        <v>-6</v>
+      </c>
+      <c r="H6">
+        <v>-1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6">
+      <c r="B7">
         <v>5</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>7</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <v>8</v>
       </c>
-      <c r="E6">
+      <c r="E7">
         <v>6</v>
       </c>
-      <c r="F6">
+      <c r="F7">
         <v>1</v>
       </c>
-      <c r="G6">
+      <c r="G7">
         <v>1</v>
       </c>
-      <c r="H6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
+      <c r="H7">
+        <v>-2</v>
+      </c>
+      <c r="I7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="B8">
         <v>-2</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>-2</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>-7</v>
       </c>
-      <c r="E7">
+      <c r="E8">
         <v>-10</v>
       </c>
-      <c r="F7">
+      <c r="F8">
         <v>-8</v>
       </c>
-      <c r="G7">
+      <c r="G8">
         <v>-2</v>
       </c>
-      <c r="H7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>-1</v>
-      </c>
-      <c r="F8">
+      <c r="H8">
         <v>-4</v>
       </c>
-      <c r="G8">
-        <v>-6</v>
-      </c>
-      <c r="H8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -3629,11 +3721,14 @@
       <c r="G9">
         <v>-8</v>
       </c>
-      <c r="H9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="H9">
+        <v>-6</v>
+      </c>
+      <c r="I9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
@@ -3655,11 +3750,14 @@
       <c r="G10">
         <v>-12</v>
       </c>
-      <c r="H10" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="H10">
+        <v>-8</v>
+      </c>
+      <c r="I10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
@@ -3681,8 +3779,11 @@
       <c r="G11">
         <v>-14</v>
       </c>
-      <c r="H11" t="s">
-        <v>94</v>
+      <c r="H11">
+        <v>-17</v>
+      </c>
+      <c r="I11" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/data/leagues/Fantasy 2026 2026.xlsx
+++ b/data/leagues/Fantasy 2026 2026.xlsx
@@ -238,25 +238,22 @@
     <t>2-5</t>
   </si>
   <si>
-    <t>9.4-4.5-0.1</t>
-  </si>
-  <si>
-    <t>9.0-4.9-0.1</t>
-  </si>
-  <si>
-    <t>8.4-5.5-0.1</t>
+    <t>9.5-4.4-0.1</t>
+  </si>
+  <si>
+    <t>9.1-4.8-0.1</t>
+  </si>
+  <si>
+    <t>8.3-5.6-0.1</t>
   </si>
   <si>
     <t>7.3-6.6-0.1</t>
   </si>
   <si>
-    <t>6.7-7.2-0.1</t>
-  </si>
-  <si>
-    <t>6.2-7.7-0.1</t>
-  </si>
-  <si>
-    <t>6.4-7.5-0.1</t>
+    <t>6.5-7.4-0.1</t>
+  </si>
+  <si>
+    <t>6.3-7.6-0.1</t>
   </si>
   <si>
     <t>5.9-8.0-0.1</t>
@@ -265,13 +262,16 @@
     <t>5.2-8.7-0.1</t>
   </si>
   <si>
-    <t>4.9-9.0-0.1</t>
+    <t>5.0-8.9-0.1</t>
   </si>
   <si>
     <t>10-4</t>
   </si>
   <si>
     <t>9-5</t>
+  </si>
+  <si>
+    <t>8-6</t>
   </si>
   <si>
     <t>7-7</t>
@@ -1877,37 +1877,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>49.5</v>
+        <v>50.9</v>
       </c>
       <c r="C2">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="D2">
-        <v>12.9</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="F2">
         <v>2.8</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H2">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="I2">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J2">
         <v>0.1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="L2">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1915,37 +1915,37 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="C3">
         <v>31.4</v>
       </c>
       <c r="D3">
-        <v>23.4</v>
+        <v>25.2</v>
       </c>
       <c r="E3">
-        <v>11.5</v>
+        <v>10.8</v>
       </c>
       <c r="F3">
-        <v>5.1</v>
+        <v>3.8</v>
       </c>
       <c r="G3">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="H3">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J3">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="K3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L3">
-        <v>98</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1953,37 +1953,37 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>21.8</v>
+        <v>19</v>
       </c>
       <c r="C4">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="D4">
-        <v>26.7</v>
+        <v>26.4</v>
       </c>
       <c r="E4">
-        <v>13.2</v>
+        <v>15.1</v>
       </c>
       <c r="F4">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="G4">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H4">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="I4">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J4">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K4">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="L4">
-        <v>94.90000000000001</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1991,37 +1991,37 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="C5">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="D5">
-        <v>12.8</v>
+        <v>13.5</v>
       </c>
       <c r="E5">
-        <v>20.7</v>
+        <v>19.3</v>
       </c>
       <c r="F5">
-        <v>20.1</v>
+        <v>17.1</v>
       </c>
       <c r="G5">
-        <v>12.8</v>
+        <v>16.1</v>
       </c>
       <c r="H5">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="I5">
         <v>6.9</v>
       </c>
       <c r="J5">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="K5">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="L5">
-        <v>75</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -2029,37 +2029,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="C6">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="D6">
-        <v>9.6</v>
+        <v>6.9</v>
       </c>
       <c r="E6">
-        <v>15.8</v>
+        <v>16.5</v>
       </c>
       <c r="F6">
-        <v>16.9</v>
+        <v>17.8</v>
       </c>
       <c r="G6">
-        <v>16</v>
+        <v>16.6</v>
       </c>
       <c r="H6">
-        <v>12.7</v>
+        <v>13.3</v>
       </c>
       <c r="I6">
-        <v>10.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6">
-        <v>6.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K6">
         <v>5.7</v>
       </c>
       <c r="L6">
-        <v>64.59999999999999</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -2067,37 +2067,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="C7">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>12.7</v>
+        <v>10.8</v>
       </c>
       <c r="F7">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="G7">
-        <v>15.3</v>
+        <v>15.7</v>
       </c>
       <c r="H7">
-        <v>13</v>
+        <v>16.1</v>
       </c>
       <c r="I7">
-        <v>16.1</v>
+        <v>13.5</v>
       </c>
       <c r="J7">
         <v>11.2</v>
       </c>
       <c r="K7">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L7">
-        <v>49.7</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -2105,37 +2105,37 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="C8">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="D8">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="E8">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
       <c r="F8">
-        <v>13.2</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="H8">
-        <v>18.6</v>
+        <v>16.1</v>
       </c>
       <c r="I8">
-        <v>15</v>
+        <v>17.9</v>
       </c>
       <c r="J8">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="K8">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L8">
-        <v>40.9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -2143,37 +2143,37 @@
         <v>3</v>
       </c>
       <c r="B9">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="C9">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="D9">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="E9">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="F9">
         <v>9.9</v>
       </c>
       <c r="G9">
-        <v>14.2</v>
+        <v>13.4</v>
       </c>
       <c r="H9">
-        <v>14.2</v>
+        <v>17</v>
       </c>
       <c r="I9">
-        <v>17.1</v>
+        <v>16.1</v>
       </c>
       <c r="J9">
-        <v>17.4</v>
+        <v>15.5</v>
       </c>
       <c r="K9">
-        <v>15.3</v>
+        <v>16.6</v>
       </c>
       <c r="L9">
-        <v>36</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2181,37 +2181,37 @@
         <v>1</v>
       </c>
       <c r="B10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="D10">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="E10">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="F10">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="G10">
-        <v>12.5</v>
+        <v>9.1</v>
       </c>
       <c r="H10">
-        <v>13.8</v>
+        <v>12.1</v>
       </c>
       <c r="I10">
-        <v>18.3</v>
+        <v>17.4</v>
       </c>
       <c r="J10">
-        <v>20.9</v>
+        <v>20.2</v>
       </c>
       <c r="K10">
-        <v>22.4</v>
+        <v>26.5</v>
       </c>
       <c r="L10">
-        <v>24.6</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -2222,34 +2222,34 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D11">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="G11">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="H11">
-        <v>12.4</v>
+        <v>10.9</v>
       </c>
       <c r="I11">
-        <v>14.4</v>
+        <v>17.6</v>
       </c>
       <c r="J11">
-        <v>21</v>
+        <v>22.7</v>
       </c>
       <c r="K11">
-        <v>35.2</v>
+        <v>30.9</v>
       </c>
       <c r="L11">
-        <v>17</v>
+        <v>17.9</v>
       </c>
     </row>
   </sheetData>
@@ -2296,25 +2296,25 @@
         <v>100</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="D2">
-        <v>99.40000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="E2">
         <v>99.8</v>
       </c>
       <c r="F2">
-        <v>99.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="G2">
-        <v>95.89999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="H2">
-        <v>99.2</v>
+        <v>99.5</v>
       </c>
       <c r="I2">
-        <v>99</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2322,28 +2322,28 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>46.40000000000001</v>
+        <v>43.7</v>
       </c>
       <c r="C3">
-        <v>96.59999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D3">
-        <v>97.59999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="E3">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="F3">
-        <v>73.2</v>
+        <v>74</v>
       </c>
       <c r="G3">
-        <v>81.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="H3">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="I3">
         <v>97.2</v>
-      </c>
-      <c r="I3">
-        <v>98.2</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2351,28 +2351,28 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>86.3</v>
+        <v>86</v>
       </c>
       <c r="C4">
-        <v>31.1</v>
+        <v>30.6</v>
       </c>
       <c r="D4">
-        <v>27.2</v>
+        <v>26.7</v>
       </c>
       <c r="E4">
-        <v>74.5</v>
+        <v>76</v>
       </c>
       <c r="F4">
-        <v>95.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G4">
-        <v>88.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="H4">
-        <v>96.89999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="I4">
-        <v>96.3</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2380,10 +2380,10 @@
         <v>9</v>
       </c>
       <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5">
         <v>99.90000000000001</v>
-      </c>
-      <c r="C5">
-        <v>100</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -2392,16 +2392,16 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>96.59999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="G5">
-        <v>90.90000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="H5">
-        <v>74.90000000000001</v>
+        <v>69.89999999999999</v>
       </c>
       <c r="I5">
-        <v>75</v>
+        <v>73.09999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2409,28 +2409,28 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>96.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="C6">
-        <v>50.4</v>
+        <v>53.3</v>
       </c>
       <c r="D6">
-        <v>86.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="E6">
-        <v>61.3</v>
+        <v>58.59999999999999</v>
       </c>
       <c r="F6">
-        <v>64.09999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="G6">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H6">
-        <v>63.6</v>
+        <v>63.1</v>
       </c>
       <c r="I6">
-        <v>64.7</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2438,86 +2438,86 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="C7">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="D7">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="E7">
-        <v>19.3</v>
+        <v>21.9</v>
       </c>
       <c r="F7">
-        <v>39.4</v>
+        <v>41.2</v>
       </c>
       <c r="G7">
-        <v>59</v>
+        <v>59.59999999999999</v>
       </c>
       <c r="H7">
-        <v>52.5</v>
+        <v>52</v>
       </c>
       <c r="I7">
-        <v>48.2</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>63.8</v>
+        <v>50.8</v>
       </c>
       <c r="C8">
-        <v>95.09999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="D8">
-        <v>89.60000000000001</v>
+        <v>34.9</v>
       </c>
       <c r="E8">
-        <v>42.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F8">
-        <v>75.90000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="G8">
-        <v>41.3</v>
+        <v>20.7</v>
       </c>
       <c r="H8">
-        <v>32.3</v>
+        <v>40.5</v>
       </c>
       <c r="I8">
-        <v>38.5</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B9">
-        <v>54.2</v>
+        <v>68.60000000000001</v>
       </c>
       <c r="C9">
-        <v>90.3</v>
+        <v>93.7</v>
       </c>
       <c r="D9">
-        <v>33.5</v>
+        <v>90.60000000000001</v>
       </c>
       <c r="E9">
-        <v>10.2</v>
+        <v>42.3</v>
       </c>
       <c r="F9">
-        <v>10.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="G9">
-        <v>20.3</v>
+        <v>44.2</v>
       </c>
       <c r="H9">
-        <v>39</v>
+        <v>32.9</v>
       </c>
       <c r="I9">
-        <v>37.8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2525,28 +2525,28 @@
         <v>1</v>
       </c>
       <c r="B10">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>28.5</v>
+        <v>27.5</v>
       </c>
       <c r="D10">
-        <v>18.7</v>
+        <v>19.9</v>
       </c>
       <c r="E10">
-        <v>34.7</v>
+        <v>34.59999999999999</v>
       </c>
       <c r="F10">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="G10">
-        <v>7.399999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="H10">
+        <v>28</v>
+      </c>
+      <c r="I10">
         <v>24</v>
-      </c>
-      <c r="I10">
-        <v>23.6</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2554,28 +2554,28 @@
         <v>7</v>
       </c>
       <c r="B11">
-        <v>49.8</v>
+        <v>52.1</v>
       </c>
       <c r="C11">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="D11">
-        <v>45.8</v>
+        <v>45.2</v>
       </c>
       <c r="E11">
         <v>58.59999999999999</v>
       </c>
       <c r="F11">
-        <v>25.2</v>
+        <v>29</v>
       </c>
       <c r="G11">
-        <v>37.2</v>
+        <v>38.1</v>
       </c>
       <c r="H11">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="I11">
-        <v>18.7</v>
+        <v>18.3</v>
       </c>
     </row>
   </sheetData>
@@ -2960,16 +2960,16 @@
         <v>917.3400000000001</v>
       </c>
       <c r="F2">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H2" t="s">
         <v>71</v>
       </c>
       <c r="I2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2989,16 +2989,16 @@
         <v>869.6999999999999</v>
       </c>
       <c r="F3">
-        <v>98</v>
+        <v>98.3</v>
       </c>
       <c r="G3">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="s">
         <v>72</v>
       </c>
       <c r="I3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3018,10 +3018,10 @@
         <v>914.5</v>
       </c>
       <c r="F4">
-        <v>94.89999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="G4">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H4" t="s">
         <v>73</v>
@@ -3047,10 +3047,10 @@
         <v>822.0800000000002</v>
       </c>
       <c r="F5">
-        <v>75</v>
+        <v>75.8</v>
       </c>
       <c r="G5">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="H5" t="s">
         <v>74</v>
@@ -3076,7 +3076,7 @@
         <v>846.58</v>
       </c>
       <c r="F6">
-        <v>64.60000000000001</v>
+        <v>63.5</v>
       </c>
       <c r="G6">
         <v>5.7</v>
@@ -3085,7 +3085,7 @@
         <v>75</v>
       </c>
       <c r="I6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3105,16 +3105,16 @@
         <v>821.02</v>
       </c>
       <c r="F7">
-        <v>49.7</v>
+        <v>50.9</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H7" t="s">
         <v>76</v>
       </c>
       <c r="I7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3134,13 +3134,13 @@
         <v>775.6399999999999</v>
       </c>
       <c r="F8">
-        <v>40.9</v>
+        <v>40</v>
       </c>
       <c r="G8">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I8" t="s">
         <v>84</v>
@@ -3163,13 +3163,13 @@
         <v>800.2600000000001</v>
       </c>
       <c r="F9">
-        <v>36</v>
+        <v>34.8</v>
       </c>
       <c r="G9">
-        <v>15.3</v>
+        <v>16.6</v>
       </c>
       <c r="H9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I9" t="s">
         <v>84</v>
@@ -3192,16 +3192,16 @@
         <v>825.4399999999999</v>
       </c>
       <c r="F10">
-        <v>24.6</v>
+        <v>23.8</v>
       </c>
       <c r="G10">
-        <v>22.4</v>
+        <v>26.5</v>
       </c>
       <c r="H10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3221,13 +3221,13 @@
         <v>814.1599999999999</v>
       </c>
       <c r="F11">
-        <v>17</v>
+        <v>17.9</v>
       </c>
       <c r="G11">
-        <v>35.2</v>
+        <v>30.9</v>
       </c>
       <c r="H11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s">
         <v>85</v>
